--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -13,12 +13,14 @@
     <sheet name="2 Brand · Generic" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="3 Brand · Master" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Assets" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Style Library" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'1 Streamer Stories'!$A$4:$U$13</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'2 Brand · Generic'!$A$4:$V$20</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'3 Brand · Master'!$A$9:$I$14</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Assets!$A$4:$I$23</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Assets!$A$4:$I$25</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Style Library'!$A$4:$G$28</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="425">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -176,7 +178,10 @@
     <t xml:space="preserve">☐  Pain-point ranking: goignon report + 10 streamer interviews (docs/USE_CASES.md §7)</t>
   </si>
   <si>
-    <t xml:space="preserve">☐  Story Fisher: tune queries, then pick the first 3 stories for tab 1</t>
+    <t xml:space="preserve">☐  Story Fisher: 12 stories shortlisted in n8n; pick the first 3 for tab 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">☐  Style rule: mixed styles from the Style Library tab, no anime/cartoon humans (docs/STYLE_DECK.md)</t>
   </si>
   <si>
     <t xml:space="preserve">☐  Product structure decision (one app vs. separate apps) before the Master script</t>
@@ -215,7 +220,7 @@
     <t xml:space="preserve">Persona</t>
   </si>
   <si>
-    <t xml:space="preserve">Art style (variety)</t>
+    <t xml:space="preserve">Style deck (home → switches)</t>
   </si>
   <si>
     <t xml:space="preserve">Song genre / tempo</t>
@@ -278,7 +283,7 @@
     <t xml:space="preserve">Starter</t>
   </si>
   <si>
-    <t xml:space="preserve">Papercut</t>
+    <t xml:space="preserve">Pixel art → Papercut · Neon line · Constellations</t>
   </si>
   <si>
     <t xml:space="preserve">Lo-fi into a hard drop, 128 BPM</t>
@@ -302,7 +307,7 @@
     <t xml:space="preserve">ST-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Anime cel</t>
+    <t xml:space="preserve">Pixel art → Papercut · Neon line · Constellations · Halftone</t>
   </si>
   <si>
     <t xml:space="preserve">30–60 s</t>
@@ -314,688 +319,994 @@
     <t xml:space="preserve">ST-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Voxel diorama → CRT/VHS · LED dot-matrix · Kinetic type · Stained glass</t>
+  </si>
+  <si>
     <t xml:space="preserve">ST-03</t>
   </si>
   <si>
-    <t xml:space="preserve">CRT / VHS</t>
+    <t xml:space="preserve">Engraving → Blueprint · Thermal · Terminal/ASCII</t>
   </si>
   <si>
     <t xml:space="preserve">ST-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Ukiyo-e print</t>
+    <t xml:space="preserve">Pixel art → CRT/VHS · Oscilloscope · Halftone</t>
   </si>
   <si>
     <t xml:space="preserve">ST-05</t>
   </si>
   <si>
-    <t xml:space="preserve">Crayon (child's drawing)</t>
+    <t xml:space="preserve">Papercut → Stained glass · Neon line · Constellations</t>
   </si>
   <si>
     <t xml:space="preserve">ST-06</t>
   </si>
   <si>
+    <t xml:space="preserve">Voxel diorama → Pixel art · Glitch · Kinetic type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neon line → LED dot-matrix · Halftone · Particles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halftone → Papercut · Blueprint · CRT/VHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 2 · Brand · Generic (pain → need → function)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One use case per film. Every film has an A version (majestic, technical, score + statements) and a B version (music video with a song). Functions marked (confirm) are assumptions until the product list arrives.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pain #</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The pain (their words)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The need</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Function shown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direction / look</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proof needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Hi?” → “Welcome back, Sam!”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Someone said hi and I didn’t see it.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never miss a newcomer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greets first-time chatters, flags them to the streamer (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A · Majestic technical: instrumental score, slow precise camera, exploded system view, one light (the companion). Deck: raymarched + blueprint → constellations · data/UI · engraving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Returning-newcomer count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9:16 first, 16:9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30–45 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B · Music video: song written from the script, pixel/voxel streamer room, kinetic word-synced lyrics. Deck: pixel or voxel → CRT · halftone · kinetic type · neon line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20–45 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 40th “what rank are you?”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grinder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Chat asks the same question 40 times.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answers without stopping play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answers FAQs in the streamer’s tone (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questions answered by the bot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raid at 2 AM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grinder, Juggler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Spam and hate raids hit when I’m alone.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protection when no mod is online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filters spam, calm raid handling, logs for mods (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Messages blocked, time to calm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U4A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 1:12 mystery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Why did everyone leave at 1:12?”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See the cause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retention report aligned with chat and stream (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insights (sub)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The aligned graph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 hours → 4 clips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part-timer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“I’d have to rewatch 4 hours of VOD.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best moments found for me</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highlights from chat spikes (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minutes saved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U6A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“What should I change?”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grinder, Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Analytics pages are just numbers.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answers, not charts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask the analyst bot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next week vs this week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U6B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U7A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The running joke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Every stream starts from zero.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Something that remembers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companion remembers regulars, jokes, milestones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companion (merged)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat reaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U7B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friday sponsor report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro, Juggler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“A sponsor wants a report by Friday.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A report I can send</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shareable report (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time from request to sent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3 · Brand · Master (one film, two versions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The whole ecosystem in one film: the companion is born (Live), remembers (Insights), grows (Companion). Built last, from the assets of sections 1 and 2. Waits for the final design and the product-structure decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quality level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Majestic technical: a new era, a second brain for every creator; scale from one desk to a planet of lit windows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental score + statements / voice-over</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60–90 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:9 hero + 9:16 cut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 7–8 (depth)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five movements below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MA-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music video: one streamer, one companion, months of streams; the song carries the story</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Song (lyrics from the script)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level 6–8 (mixed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same beats, different sound and pace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movement breakdown (draft for discussion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Picture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A · statement (draft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B · lyric idea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pain / layer shown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One streamer, one screen in the dark; pull back through the window to a city, then a planet of lit windows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Every night, millions create alone.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The empty chat, the quiet room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pains 1, 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streamer room, planet of windows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One window turns warm: the companion is born, free and open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Until now.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hook: the first hello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companion stage 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flythrough of the system: live chat → stream data → reports → memory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“It listens. It learns. It remembers.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verse: what it does for you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploded system view, UI stand-ins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The second brain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The memory ring grows into a constellation around the streamer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“Not a tool. A second brain.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridge: it remembers your people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companion stages 2–3, constellation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A new era</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window after window lights warm; the logo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">“A companion for every creator.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final chorus + sonic logo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End card, sonic logo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built once, used by every section. Everything is code-rendered unless the source says otherwise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depends on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand palette tokens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your web design → one palette file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placeholder until the design lands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonts (display + mono)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your web design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logo (SVG) + wordmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logo, palette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same in every video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonic logo (2 s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music partner / Suno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ends every video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companion · stage 1 (spark)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companion · stage 2 (memory ring)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic, Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Companion · stage 3 (full form)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merged companion; mascot art if you have one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streamer (silhouette, hoodie, headset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No face, so anyone sees themselves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streamer as pixel / voxel sprite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stories, Generic B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code (32×32 or 64×64 sprite)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No anime or cartoon humans (docs/STYLE_DECK.md)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Style deck shaders (A-tier styles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code, one file per style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built once, reused by every film; see the Style Library tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set · streamer’s room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic B, Master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitor light, window god rays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set · planet / city of windows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic A, Master A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hero shot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploded system view</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live → data → Insights → memory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat UI (generic, ours)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never a real platform’s UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product UI screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your web design (stand-ins until then)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Story Fisher (n8n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n8n workflow JuU4QgIrT1o10zO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brave + PullPush + DeepSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built; queries being tuned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Songs (one per film)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stories, Generic B, Master B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You (Suno / partner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approved script</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written to the approved script</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scores (A versions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voice-over (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disclose if AI voice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proof: beta user numbers + quotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No invented numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Style library · what we render well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every film mixes styles: one home style + 3–5 switch styles from tier A, switching on the music. No anime/cartoon humans. Rules: docs/STYLE_DECK.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Characters in it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hold length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel art</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A · use freely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home style for stories; the streamer and chat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel sprites, mascot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proven on the Venmar × Quest film</t>
+  </si>
+  <si>
     <t xml:space="preserve">Voxel diorama</t>
   </si>
   <si>
-    <t xml:space="preserve">ST-07</t>
+    <t xml:space="preserve">Home style; rooms and cities as toys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voxel sprites, mascot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proven: voxel rig + move library exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRT / VHS / glitch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pain moments, flashbacks, the 'cold' look</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any (it filters the frame)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–4 bars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED dot-matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hooks, numbers, chat messages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mascot, text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beats–2 bars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal / ASCII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The bot's point of view, data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text, mascot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–2 bars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blueprint / technical drawing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How it works; Generic A, Master A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silhouettes, mascot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–8 bars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engraving / line hatching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sad or serious stories; majestic A versions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silhouettes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pdoom's strongest look</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscilloscope / vector glow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music-reactive moments, the voice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lines, mascot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Newspaper halftone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headlines, big moments ('RAIDED!')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silhouettes, text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papercut (flat layers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wholesome stories, warm scenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple shapes, mascot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–4 bars</t>
   </si>
   <si>
     <t xml:space="preserve">Stained glass</t>
   </si>
   <si>
-    <t xml:space="preserve">ST-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Newspaper halftone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Section 2 · Brand · Generic (pain → need → function)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One use case per film. Every film has an A version (majestic, technical, score + statements) and a B version (music video with a song). Functions marked (confirm) are assumptions until the product list arrives.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pain #</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The pain (their words)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The need</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Function shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direction / look</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proof needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Hi?” → “Welcome back, Sam!”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Someone said hi and I didn’t see it.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Never miss a newcomer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greets first-time chatters, flags them to the streamer (confirm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A · Majestic technical: instrumental score, slow precise camera, exploded system view, one light (the companion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Returning-newcomer count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9:16 first, 16:9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30–45 s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B · Music video: song written from the script, the streamer’s room, kinetic word-synced lyrics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20–45 s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 40th “what rank are you?”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grinder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Chat asks the same question 40 times.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Answers without stopping play</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Answers FAQs in the streamer’s tone (confirm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questions answered by the bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raid at 2 AM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grinder, Juggler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Spam and hate raids hit when I’m alone.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protection when no mod is online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filters spam, calm raid handling, logs for mods (confirm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Messages blocked, time to calm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U4A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The 1:12 mystery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Why did everyone leave at 1:12?”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See the cause</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retention report aligned with chat and stream (confirm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insights (sub)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The aligned graph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 hours → 4 clips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part-timer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“I’d have to rewatch 4 hours of VOD.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best moments found for me</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highlights from chat spikes (confirm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minutes saved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U6A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“What should I change?”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grinder, Pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Analytics pages are just numbers.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Answers, not charts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask the analyst bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next week vs this week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U6B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The running joke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Every stream starts from zero.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Something that remembers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Companion remembers regulars, jokes, milestones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Companion (merged)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chat reaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U7B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U8A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friday sponsor report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro, Juggler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“A sponsor wants a report by Friday.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A report I can send</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shareable report (confirm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time from request to sent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GN-U8B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Section 3 · Brand · Master (one film, two versions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The whole ecosystem in one film: the companion is born (Live), remembers (Insights), grows (Companion). Built last, from the assets of sections 1 and 2. Waits for the final design and the product-structure decision.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MA-A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Majestic technical: a new era, a second brain for every creator; scale from one desk to a planet of lit windows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instrumental score + statements / voice-over</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60–90 s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:9 hero + 9:16 cut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 7–8 (depth)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Five movements below</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MA-B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Music video: one streamer, one companion, months of streams; the song carries the story</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Song (lyrics from the script)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level 6–8 (mixed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same beats, different sound and pace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movement breakdown (draft for discussion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Picture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A · statement (draft)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B · lyric idea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pain / layer shown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One streamer, one screen in the dark; pull back through the window to a city, then a planet of lit windows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Every night, millions create alone.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The empty chat, the quiet room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pains 1, 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streamer room, planet of windows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One window turns warm: the companion is born, free and open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Until now.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hook: the first hello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Companion stage 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The architecture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flythrough of the system: live chat → stream data → reports → memory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“It listens. It learns. It remembers.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verse: what it does for you</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exploded system view, UI stand-ins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The second brain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The memory ring grows into a constellation around the streamer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“Not a tool. A second brain.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bridge: it remembers your people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Companion stages 2–3, constellation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A new era</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window after window lights warm; the logo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“A companion for every creator.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final chorus + sonic logo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End card, sonic logo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shared assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built once, used by every section. Everything is code-rendered unless the source says otherwise.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Used by</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depends on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Due</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand palette tokens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your web design → one palette file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Web design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placeholder until the design lands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonts (display + mono)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your web design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logo (SVG) + wordmark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End card</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logo, palette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same in every video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonic logo (2 s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Music partner / Suno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ends every video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Companion · stage 1 (spark)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Character</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live app</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Companion · stage 2 (memory ring)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic, Master</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stage 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Companion · stage 3 (full form)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stage 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merged companion; mascot art if you have one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Streamer (silhouette, hoodie, headset)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No face, so anyone sees themselves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set · streamer’s room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic B, Master</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitor light, window god rays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set · planet / city of windows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic A, Master A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hero shot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exploded system view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live → data → Insights → memory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chat UI (generic, ours)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Never a real platform’s UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product UI screens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Your web design (stand-ins until then)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Story Fisher (n8n)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipeline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n8n workflow JuU4QgIrT1o10zO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brave + PullPush + DeepSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built; queries being tuned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Songs (one per film)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stories, Generic B, Master B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You (Suno / partner)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approved script</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Written to the approved script</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scores (A versions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instrumental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voice-over (optional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disclose if AI voice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proof: beta user numbers + quotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beta users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No invented numbers</t>
+    <t xml:space="preserve">Triumphant moments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neon line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Night streams, energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thermal camera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tension, the 'who is watching' feeling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data / UI / charts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insights, reports, Generic films</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real UI once the design lands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinetic typography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyrics, statements, hooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always on top of the other styles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particles / constellations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memory, the second brain, the drop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mascot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstract raymarched objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Majestic A versions, hero shots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None (objects only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–16 bars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPU-heavy at 4K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukiyo-e waves / patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B · short holds / backgrounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backgrounds, transitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No figures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤ 1 bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ink wash (abstract)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transitions, emotion beats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watercolor washes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft backgrounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤ 2 bars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crayon texture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 'drawn by a kid' flash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple shapes only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isometric rooms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Establishing shots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel/voxel only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anime / cartoon humans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C · avoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four attempts failed on the Venmar branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realistic faces / photoreal people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reads as AI-made</t>
   </si>
 </sst>
 </file>
@@ -1289,7 +1600,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1379,6 +1690,38 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD5F2DC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8D3D3"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE7B3"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEEEEEE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -1431,7 +1774,7 @@
       <rgbColor rgb="FF5B6170"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF2BB673"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -1456,6 +1799,10 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -1922,9 +2269,14 @@
         <v>50</v>
       </c>
     </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1953,7 +2305,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
@@ -1968,115 +2320,115 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M5" s="17" t="s">
         <v>39</v>
@@ -2095,16 +2447,16 @@
       </c>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T5" s="17"/>
       <c r="U5" s="17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2113,14 +2465,14 @@
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
       <c r="H6" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I6" s="18"/>
       <c r="J6" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L6" s="18"/>
       <c r="M6" s="5" t="s">
@@ -2142,12 +2494,12 @@
       <c r="S6" s="5"/>
       <c r="T6" s="18"/>
       <c r="U6" s="18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -2156,14 +2508,14 @@
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
       <c r="H7" s="5" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I7" s="18"/>
       <c r="J7" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L7" s="18"/>
       <c r="M7" s="5" t="s">
@@ -2185,12 +2537,12 @@
       <c r="S7" s="5"/>
       <c r="T7" s="18"/>
       <c r="U7" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -2199,14 +2551,14 @@
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
       <c r="H8" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L8" s="18"/>
       <c r="M8" s="5" t="s">
@@ -2228,12 +2580,12 @@
       <c r="S8" s="5"/>
       <c r="T8" s="18"/>
       <c r="U8" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -2242,14 +2594,14 @@
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
       <c r="H9" s="5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L9" s="18"/>
       <c r="M9" s="5" t="s">
@@ -2271,12 +2623,12 @@
       <c r="S9" s="5"/>
       <c r="T9" s="18"/>
       <c r="U9" s="18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -2285,14 +2637,14 @@
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
       <c r="H10" s="5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I10" s="18"/>
       <c r="J10" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L10" s="18"/>
       <c r="M10" s="5" t="s">
@@ -2314,12 +2666,12 @@
       <c r="S10" s="5"/>
       <c r="T10" s="18"/>
       <c r="U10" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -2328,14 +2680,14 @@
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L11" s="18"/>
       <c r="M11" s="5" t="s">
@@ -2357,12 +2709,12 @@
       <c r="S11" s="5"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -2371,14 +2723,14 @@
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="5" t="s">
@@ -2400,12 +2752,12 @@
       <c r="S12" s="5"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -2414,14 +2766,14 @@
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
       <c r="H13" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L13" s="18"/>
       <c r="M13" s="5" t="s">
@@ -2443,7 +2795,7 @@
       <c r="S13" s="5"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2612,122 +2964,122 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K5" s="18"/>
       <c r="L5" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>38</v>
@@ -2748,46 +3100,46 @@
       <c r="U5" s="18"/>
       <c r="V5" s="18"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K6" s="18"/>
       <c r="L6" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>38</v>
@@ -2808,46 +3160,46 @@
       <c r="U6" s="18"/>
       <c r="V6" s="18"/>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K7" s="18"/>
       <c r="L7" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>38</v>
@@ -2868,46 +3220,46 @@
       <c r="U7" s="18"/>
       <c r="V7" s="18"/>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>140</v>
-      </c>
       <c r="I8" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>38</v>
@@ -2928,46 +3280,46 @@
       <c r="U8" s="18"/>
       <c r="V8" s="18"/>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K9" s="18"/>
       <c r="L9" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>38</v>
@@ -2988,46 +3340,46 @@
       <c r="U9" s="18"/>
       <c r="V9" s="18"/>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="I10" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K10" s="18"/>
       <c r="L10" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>38</v>
@@ -3048,46 +3400,46 @@
       <c r="U10" s="18"/>
       <c r="V10" s="18"/>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K11" s="18"/>
       <c r="L11" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>38</v>
@@ -3108,46 +3460,46 @@
       <c r="U11" s="18"/>
       <c r="V11" s="18"/>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>158</v>
-      </c>
       <c r="J12" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K12" s="18"/>
       <c r="L12" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>38</v>
@@ -3168,46 +3520,46 @@
       <c r="U12" s="18"/>
       <c r="V12" s="18"/>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K13" s="18"/>
       <c r="L13" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>38</v>
@@ -3228,46 +3580,46 @@
       <c r="U13" s="18"/>
       <c r="V13" s="18"/>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>167</v>
-      </c>
       <c r="I14" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K14" s="18"/>
       <c r="L14" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O14" s="5" t="s">
         <v>38</v>
@@ -3288,46 +3640,46 @@
       <c r="U14" s="18"/>
       <c r="V14" s="18"/>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K15" s="18"/>
       <c r="L15" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>38</v>
@@ -3348,46 +3700,46 @@
       <c r="U15" s="18"/>
       <c r="V15" s="18"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>176</v>
-      </c>
       <c r="I16" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K16" s="18"/>
       <c r="L16" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>38</v>
@@ -3408,46 +3760,46 @@
       <c r="U16" s="18"/>
       <c r="V16" s="18"/>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K17" s="18"/>
       <c r="L17" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>38</v>
@@ -3468,46 +3820,46 @@
       <c r="U17" s="18"/>
       <c r="V17" s="18"/>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="J18" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O18" s="5" t="s">
         <v>38</v>
@@ -3528,46 +3880,46 @@
       <c r="U18" s="18"/>
       <c r="V18" s="18"/>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>38</v>
@@ -3588,46 +3940,46 @@
       <c r="U19" s="18"/>
       <c r="V19" s="18"/>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="I20" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K20" s="18"/>
       <c r="L20" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O20" s="5" t="s">
         <v>38</v>
@@ -3809,82 +4161,82 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>38</v>
@@ -3904,30 +4256,30 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="18" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>38</v>
@@ -3947,41 +4299,41 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="18" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3989,22 +4341,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>38</v>
@@ -4016,22 +4368,22 @@
         <v>2</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>38</v>
@@ -4043,22 +4395,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>38</v>
@@ -4070,22 +4422,22 @@
         <v>4</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>38</v>
@@ -4097,22 +4449,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>38</v>
@@ -4284,7 +4636,7 @@
     <tabColor rgb="FF5B6170"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -4300,58 +4652,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>38</v>
@@ -4359,24 +4711,24 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>261</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>38</v>
@@ -4387,16 +4739,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
@@ -4408,19 +4760,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>38</v>
@@ -4428,21 +4780,21 @@
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
       <c r="I8" s="18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
@@ -4451,24 +4803,24 @@
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>38</v>
@@ -4476,24 +4828,24 @@
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>38</v>
@@ -4501,24 +4853,24 @@
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>279</v>
-      </c>
       <c r="D12" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>38</v>
@@ -4526,21 +4878,21 @@
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
@@ -4549,21 +4901,21 @@
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
@@ -4572,21 +4924,21 @@
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>291</v>
+        <v>183</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
@@ -4595,172 +4947,168 @@
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>294</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>297</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>181</v>
+        <v>301</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>276</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>297</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="I18" s="18" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>303</v>
+        <v>183</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="C20" s="5" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>310</v>
+        <v>263</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
-      <c r="I20" s="18" t="s">
-        <v>311</v>
-      </c>
+      <c r="I20" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="C21" s="5" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>38</v>
@@ -4768,35 +5116,85 @@
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>318</v>
+        <v>202</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18" t="s">
-        <v>321</v>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I23"/>
-  <conditionalFormatting sqref="F5:F23">
+  <autoFilter ref="A4:I25"/>
+  <conditionalFormatting sqref="F5:F25">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>F5="Not started"</formula>
     </cfRule>
@@ -4817,7 +5215,628 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F23" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F25" type="list">
+      <formula1>"Not started,In progress,Review,Approved,Blocked,N/A"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF2BB673"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>424</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G28"/>
+  <conditionalFormatting sqref="F5:F28">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>F5="Not started"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>F5="In progress"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>F5="Review"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>F5="Approved"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>F5="Blocked"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>F5="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B28">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>B5="A · use freely"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>B5="B · short holds / backgrounds"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>B5="C · avoid"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F28" type="list">
       <formula1>"Not started,In progress,Review,Approved,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -14,6 +14,7 @@
     <sheet name="3 Brand · Master" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Assets" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Style Library" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Effort Levels" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'1 Streamer Stories'!$A$4:$U$13</definedName>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="514">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -1307,16 +1308,303 @@
   </si>
   <si>
     <t xml:space="preserve">Reads as AI-made</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effort levels · what each level costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levels from the medium-lens-film skill (07_quality_levels.md). Hours are Opus agent-hours of building, estimates until the first film is calibrated. Blue cells are inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Looks like</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendering added at this level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent-hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final render (GPU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean synced motion graphics, one look</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloom, grain, flash/shake on hits, word-synced type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3–4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minutes (1080p)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple 3D lit properly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soft shadows, ambient occlusion, real materials, depth of field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ atmosphere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fog, god rays, rain on glass, wet reflections, secondary motion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5–6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low–medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studio ad; mixed style deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bounce light, PBR bloom, flares, lens dirt; 3–5 switch styles + material transitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6–7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dressed sets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 fully dressed environments, lit particles, mosaic of styles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7–8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinematic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volumetric sky/light, 60 fps adaptive motion blur, 1 hero shot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8–10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium–high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feels shot on film</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Film grain, halation, gate weave, grade per shot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10–11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camera choreography per shot, a material transition on every cut, nested pull-back ending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11–13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloth, smoke/ink, voxel destruction, crowds of chat bubbles, sound design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13–14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S++</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2430"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">《光先到》 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2430"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ pdoom 4K</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Every shot a hero shot, 4K60 path-traced look</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14–16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very high (20–60+ GPU-h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan rates (% of a weekly allowance per agent-hour, incl. +30% rework; replace with your own after calibration)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max 5×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max 20×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: medium-lens-film skill, references/07_quality_levels.md (branch claude/zealous-newton-7zpeja). Estimates, not measurements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effort by film (first wave)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Film(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hours total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max 5× weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max 20× weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why this level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-01 (first story)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 · B mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Builds the shared style-deck shaders, the pixel/voxel streamer and kinetic type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-02 … ST-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuses the deck shaders; new story, song timing, style picks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U1A (first A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 · A depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Builds the majestic sets: system view, constellations, sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U2A … U8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuses the A sets; new use case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U1B (first B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 · B+ mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Builds the streamer room in pixel/voxel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GN-U2B … U8B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuses the room and the deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 · S depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The hero film: camera choreography, nested pull-back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 · A+ mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same beats as A, reuses its assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weeks = weekly allowances used (1.0 = one full week of that plan). Calibrate on ST-01: note the usage bar before and after, then replace the rates above.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1402,8 +1690,29 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2430"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F2430"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1437,7 +1746,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCEBFF"/>
-        <bgColor rgb="FFEEEEEE"/>
+        <bgColor rgb="FFE9ECF2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1461,7 +1770,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEEEE"/>
-        <bgColor rgb="FFF3F3F3"/>
+        <bgColor rgb="FFE9ECF2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9ECF2"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1514,7 +1829,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1589,6 +1904,34 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1739,7 +2082,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFF3F3F3"/>
+      <rgbColor rgb="FFEEEEEE"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -1747,7 +2090,7 @@
       <rgbColor rgb="FFDCEBFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF0F6FDE"/>
       <rgbColor rgb="FFC9CED8"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -1758,10 +2101,10 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFEEEEEE"/>
+      <rgbColor rgb="FFE9ECF2"/>
       <rgbColor rgb="FFD5F2DC"/>
       <rgbColor rgb="FFFFE7B3"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFF3F3F3"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFF8D3D3"/>
@@ -5850,4 +6193,658 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF0F6FDE"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="62"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="B17" s="21" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="B18" s="21" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>0.0033</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <f aca="false">D24*E24</f>
+        <v>6.5</v>
+      </c>
+      <c r="G24" s="23" t="n">
+        <f aca="false">F24*$B$17</f>
+        <v>0.4225</v>
+      </c>
+      <c r="H24" s="23" t="n">
+        <f aca="false">F24*$B$18</f>
+        <v>0.0845</v>
+      </c>
+      <c r="I24" s="23" t="n">
+        <f aca="false">F24*$B$19</f>
+        <v>0.02145</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <f aca="false">D25*E25</f>
+        <v>17.5</v>
+      </c>
+      <c r="G25" s="23" t="n">
+        <f aca="false">F25*$B$17</f>
+        <v>1.1375</v>
+      </c>
+      <c r="H25" s="23" t="n">
+        <f aca="false">F25*$B$18</f>
+        <v>0.2275</v>
+      </c>
+      <c r="I25" s="23" t="n">
+        <f aca="false">F25*$B$19</f>
+        <v>0.05775</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <f aca="false">D26*E26</f>
+        <v>9</v>
+      </c>
+      <c r="G26" s="23" t="n">
+        <f aca="false">F26*$B$17</f>
+        <v>0.585</v>
+      </c>
+      <c r="H26" s="23" t="n">
+        <f aca="false">F26*$B$18</f>
+        <v>0.117</v>
+      </c>
+      <c r="I26" s="23" t="n">
+        <f aca="false">F26*$B$19</f>
+        <v>0.0297</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <f aca="false">D27*E27</f>
+        <v>24.5</v>
+      </c>
+      <c r="G27" s="23" t="n">
+        <f aca="false">F27*$B$17</f>
+        <v>1.5925</v>
+      </c>
+      <c r="H27" s="23" t="n">
+        <f aca="false">F27*$B$18</f>
+        <v>0.3185</v>
+      </c>
+      <c r="I27" s="23" t="n">
+        <f aca="false">F27*$B$19</f>
+        <v>0.08085</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <f aca="false">D28*E28</f>
+        <v>4</v>
+      </c>
+      <c r="G28" s="23" t="n">
+        <f aca="false">F28*$B$17</f>
+        <v>0.26</v>
+      </c>
+      <c r="H28" s="23" t="n">
+        <f aca="false">F28*$B$18</f>
+        <v>0.052</v>
+      </c>
+      <c r="I28" s="23" t="n">
+        <f aca="false">F28*$B$19</f>
+        <v>0.0132</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <f aca="false">D29*E29</f>
+        <v>17.5</v>
+      </c>
+      <c r="G29" s="23" t="n">
+        <f aca="false">F29*$B$17</f>
+        <v>1.1375</v>
+      </c>
+      <c r="H29" s="23" t="n">
+        <f aca="false">F29*$B$18</f>
+        <v>0.2275</v>
+      </c>
+      <c r="I29" s="23" t="n">
+        <f aca="false">F29*$B$19</f>
+        <v>0.05775</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <f aca="false">D30*E30</f>
+        <v>12</v>
+      </c>
+      <c r="G30" s="23" t="n">
+        <f aca="false">F30*$B$17</f>
+        <v>0.78</v>
+      </c>
+      <c r="H30" s="23" t="n">
+        <f aca="false">F30*$B$18</f>
+        <v>0.156</v>
+      </c>
+      <c r="I30" s="23" t="n">
+        <f aca="false">F30*$B$19</f>
+        <v>0.0396</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <f aca="false">D31*E31</f>
+        <v>7</v>
+      </c>
+      <c r="G31" s="23" t="n">
+        <f aca="false">F31*$B$17</f>
+        <v>0.455</v>
+      </c>
+      <c r="H31" s="23" t="n">
+        <f aca="false">F31*$B$18</f>
+        <v>0.091</v>
+      </c>
+      <c r="I31" s="23" t="n">
+        <f aca="false">F31*$B$19</f>
+        <v>0.0231</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24" t="s">
+        <v>512</v>
+      </c>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24" t="n">
+        <f aca="false">SUM(D24:D31)</f>
+        <v>26</v>
+      </c>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24" t="n">
+        <f aca="false">SUM(F24:F31)</f>
+        <v>98</v>
+      </c>
+      <c r="G32" s="25" t="n">
+        <f aca="false">SUM(G24:G31)</f>
+        <v>6.37</v>
+      </c>
+      <c r="H32" s="25" t="n">
+        <f aca="false">SUM(H24:H31)</f>
+        <v>1.274</v>
+      </c>
+      <c r="I32" s="25" t="n">
+        <f aca="false">SUM(I24:I31)</f>
+        <v>0.3234</v>
+      </c>
+      <c r="J32" s="24"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
+        <v>513</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="522">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -308,19 +308,43 @@
     <t xml:space="preserve">ST-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Pixel art → Papercut · Neon line · Constellations · Halftone</t>
+    <t xml:space="preserve">The train ride (TEST film, level 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/r/Twitch/comments/1pujw7y/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A desk-bound game streamer streams IRL at Christmas, peaks at 3 viewers; one viewer watches the train ride until the signal drops, then says it was amazing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8, 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel art → Neon line · Halftone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm lo-fi indie pop, 120 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anonymised retelling; ask the author before publishing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Script: docs/scripts/ST-01_train-ride.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voxel diorama → CRT/VHS · LED dot-matrix · Kinetic type · Stained glass</t>
   </si>
   <si>
     <t xml:space="preserve">30–60 s</t>
   </si>
   <si>
     <t xml:space="preserve">Pick from the Story Fisher shortlist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voxel diorama → CRT/VHS · LED dot-matrix · Kinetic type · Stained glass</t>
   </si>
   <si>
     <t xml:space="preserve">ST-03</t>
@@ -1993,6 +2017,14 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE7B3"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
@@ -2045,14 +2077,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8D3D3"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFE7B3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2797,29 +2821,45 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="B6" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>82</v>
+      </c>
       <c r="H6" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="18"/>
+        <v>95</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>96</v>
+      </c>
       <c r="J6" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="L6" s="18"/>
+        <v>97</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>98</v>
+      </c>
       <c r="M6" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>38</v>
@@ -2834,15 +2874,17 @@
         <v>38</v>
       </c>
       <c r="R6" s="18"/>
-      <c r="S6" s="5"/>
+      <c r="S6" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="T6" s="18"/>
       <c r="U6" s="18" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -2851,14 +2893,14 @@
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
       <c r="H7" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="I7" s="18"/>
       <c r="J7" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L7" s="18"/>
       <c r="M7" s="5" t="s">
@@ -2880,12 +2922,12 @@
       <c r="S7" s="5"/>
       <c r="T7" s="18"/>
       <c r="U7" s="18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -2894,14 +2936,14 @@
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
       <c r="H8" s="5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L8" s="18"/>
       <c r="M8" s="5" t="s">
@@ -2923,12 +2965,12 @@
       <c r="S8" s="5"/>
       <c r="T8" s="18"/>
       <c r="U8" s="18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -2937,14 +2979,14 @@
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
       <c r="H9" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L9" s="18"/>
       <c r="M9" s="5" t="s">
@@ -2966,12 +3008,12 @@
       <c r="S9" s="5"/>
       <c r="T9" s="18"/>
       <c r="U9" s="18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -2980,14 +3022,14 @@
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
       <c r="H10" s="5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I10" s="18"/>
       <c r="J10" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L10" s="18"/>
       <c r="M10" s="5" t="s">
@@ -3009,12 +3051,12 @@
       <c r="S10" s="5"/>
       <c r="T10" s="18"/>
       <c r="U10" s="18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -3023,14 +3065,14 @@
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L11" s="18"/>
       <c r="M11" s="5" t="s">
@@ -3052,12 +3094,12 @@
       <c r="S11" s="5"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -3066,14 +3108,14 @@
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="5" t="s">
@@ -3095,12 +3137,12 @@
       <c r="S12" s="5"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -3109,14 +3151,14 @@
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
       <c r="H13" s="5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="L13" s="18"/>
       <c r="M13" s="5" t="s">
@@ -3138,108 +3180,108 @@
       <c r="S13" s="5"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:U13"/>
   <conditionalFormatting sqref="M5:M13">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>M5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>M5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>M5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>M5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>M5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>M5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:N13">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>N5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>N5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>N5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>N5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>N5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>N5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O5:O13">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>O5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>O5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>O5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>O5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>O5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>O5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P13">
-    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>P5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>P5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>P5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>P5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>P5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>P5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q13">
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>Q5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>Q5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>Q5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>Q5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>Q5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>Q5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3307,12 +3349,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3320,37 +3362,37 @@
         <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>64</v>
@@ -3385,44 +3427,44 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K5" s="18"/>
       <c r="L5" s="5" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>38</v>
@@ -3445,44 +3487,44 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K6" s="18"/>
       <c r="L6" s="5" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>38</v>
@@ -3505,44 +3547,44 @@
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="K7" s="18"/>
       <c r="L7" s="5" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>38</v>
@@ -3565,44 +3607,44 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>134</v>
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>38</v>
@@ -3625,44 +3667,44 @@
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K9" s="18"/>
       <c r="L9" s="5" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>38</v>
@@ -3685,44 +3727,44 @@
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K10" s="18"/>
       <c r="L10" s="5" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>38</v>
@@ -3745,44 +3787,44 @@
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K11" s="18"/>
       <c r="L11" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>38</v>
@@ -3805,44 +3847,44 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K12" s="18"/>
       <c r="L12" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>38</v>
@@ -3865,44 +3907,44 @@
     </row>
     <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G13" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>160</v>
-      </c>
       <c r="J13" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K13" s="18"/>
       <c r="L13" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>38</v>
@@ -3925,44 +3967,44 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G14" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>160</v>
-      </c>
       <c r="J14" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K14" s="18"/>
       <c r="L14" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O14" s="5" t="s">
         <v>38</v>
@@ -3985,44 +4027,44 @@
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K15" s="18"/>
       <c r="L15" s="5" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>38</v>
@@ -4045,44 +4087,44 @@
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K16" s="18"/>
       <c r="L16" s="5" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>38</v>
@@ -4105,44 +4147,44 @@
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K17" s="18"/>
       <c r="L17" s="5" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>38</v>
@@ -4165,44 +4207,44 @@
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>182</v>
-      </c>
       <c r="D18" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="5" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O18" s="5" t="s">
         <v>38</v>
@@ -4225,44 +4267,44 @@
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="5" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>38</v>
@@ -4285,44 +4327,44 @@
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K20" s="18"/>
       <c r="L20" s="5" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O20" s="5" t="s">
         <v>38</v>
@@ -4346,102 +4388,102 @@
   </sheetData>
   <autoFilter ref="A4:V20"/>
   <conditionalFormatting sqref="O5:O20">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>O5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>O5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>O5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>O5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>O5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>O5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P20">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>P5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>P5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>P5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>P5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>P5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>P5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q20">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>Q5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>Q5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>Q5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>Q5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>Q5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>Q5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R5:R20">
-    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>R5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>R5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>R5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>R5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>R5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>R5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S5:S20">
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>S5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>S5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>S5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>S5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>S5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>S5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4504,12 +4546,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4517,13 +4559,13 @@
         <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>65</v>
@@ -4532,7 +4574,7 @@
         <v>64</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>67</v>
@@ -4561,25 +4603,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>38</v>
@@ -4599,30 +4641,30 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="18" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>38</v>
@@ -4642,38 +4684,38 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="18" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>75</v>
@@ -4684,22 +4726,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>38</v>
@@ -4711,22 +4753,22 @@
         <v>2</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>38</v>
@@ -4738,22 +4780,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>38</v>
@@ -4765,22 +4807,22 @@
         <v>4</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>38</v>
@@ -4792,22 +4834,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>38</v>
@@ -4817,122 +4859,122 @@
   </sheetData>
   <autoFilter ref="A9:I14"/>
   <conditionalFormatting sqref="H5:H6">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>H5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>H5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>H5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>H5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>H5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>H5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I6">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>I5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>I5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>I5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>I5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>I5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>I5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:J6">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>J5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>J5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>J5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>J5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>J5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>J5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K6">
-    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>K5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>K5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>K5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>K5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>K5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>K5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L6">
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>L5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>L5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>L5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>L5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>L5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>L5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H10:H14">
-    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>H10="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>H10="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>H10="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>H10="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>H10="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>H10="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4995,38 +5037,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>74</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>75</v>
@@ -5034,19 +5076,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>38</v>
@@ -5054,24 +5096,24 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>38</v>
@@ -5082,16 +5124,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
@@ -5103,19 +5145,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>261</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>38</v>
@@ -5123,21 +5165,21 @@
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
       <c r="I8" s="18" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
@@ -5146,24 +5188,24 @@
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>38</v>
@@ -5171,24 +5213,24 @@
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>38</v>
@@ -5196,24 +5238,24 @@
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>38</v>
@@ -5221,21 +5263,21 @@
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
@@ -5244,21 +5286,21 @@
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
@@ -5267,21 +5309,21 @@
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
@@ -5290,21 +5332,21 @@
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
@@ -5313,21 +5355,21 @@
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
@@ -5336,24 +5378,24 @@
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>38</v>
@@ -5361,24 +5403,24 @@
       <c r="G18" s="18"/>
       <c r="H18" s="18"/>
       <c r="I18" s="18" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>38</v>
@@ -5386,24 +5428,24 @@
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>38</v>
@@ -5414,19 +5456,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>39</v>
@@ -5434,24 +5476,24 @@
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>38</v>
@@ -5459,24 +5501,24 @@
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>38</v>
@@ -5484,24 +5526,24 @@
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>38</v>
@@ -5509,21 +5551,21 @@
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
@@ -5532,28 +5574,28 @@
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:I25"/>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>F5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>F5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>F5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>F5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>F5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>F5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5594,32 +5636,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>75</v>
@@ -5627,65 +5669,65 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>38</v>
@@ -5694,19 +5736,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>38</v>
@@ -5715,19 +5757,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>38</v>
@@ -5736,19 +5778,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>38</v>
@@ -5757,42 +5799,42 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>38</v>
@@ -5801,19 +5843,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>38</v>
@@ -5822,19 +5864,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>38</v>
@@ -5843,19 +5885,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>38</v>
@@ -5864,19 +5906,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>38</v>
@@ -5885,19 +5927,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>38</v>
@@ -5906,65 +5948,65 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>38</v>
@@ -5973,42 +6015,42 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>38</v>
@@ -6017,19 +6059,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>38</v>
@@ -6038,19 +6080,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>38</v>
@@ -6059,19 +6101,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>415</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>407</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>38</v>
@@ -6080,19 +6122,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>38</v>
@@ -6101,80 +6143,80 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:G28"/>
   <conditionalFormatting sqref="F5:F28">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>F5="Not started"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>F5="In progress"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>F5="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>F5="Approved"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>F5="Blocked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>F5="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B28">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>B5="A · use freely"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>B5="B · short holds / backgrounds"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>B5="C · avoid"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6217,32 +6259,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6250,19 +6292,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6270,19 +6312,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6290,19 +6332,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6310,19 +6352,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6330,19 +6372,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6350,19 +6392,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6370,19 +6412,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6390,19 +6432,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6410,19 +6452,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6430,29 +6472,29 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>0.065</v>
@@ -6460,7 +6502,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>0.013</v>
@@ -6468,7 +6510,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>0.0033</v>
@@ -6476,55 +6518,55 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D24" s="22" t="n">
         <v>1</v>
@@ -6549,18 +6591,18 @@
         <v>0.02145</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D25" s="22" t="n">
         <v>7</v>
@@ -6585,18 +6627,18 @@
         <v>0.05775</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D26" s="22" t="n">
         <v>1</v>
@@ -6621,18 +6663,18 @@
         <v>0.0297</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D27" s="22" t="n">
         <v>7</v>
@@ -6657,18 +6699,18 @@
         <v>0.08085</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D28" s="22" t="n">
         <v>1</v>
@@ -6693,18 +6735,18 @@
         <v>0.0132</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D29" s="22" t="n">
         <v>7</v>
@@ -6729,18 +6771,18 @@
         <v>0.05775</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="D30" s="22" t="n">
         <v>1</v>
@@ -6765,18 +6807,18 @@
         <v>0.0396</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D31" s="22" t="n">
         <v>1</v>
@@ -6801,12 +6843,12 @@
         <v>0.0231</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="24" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="24"/>
@@ -6835,7 +6877,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="521">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">ST-01</t>
   </si>
   <si>
-    <t xml:space="preserve">The train ride (TEST film, level 3)</t>
+    <t xml:space="preserve">The train ride (first film, level 6)</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.reddit.com/r/Twitch/comments/1pujw7y/</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">Effort levels · what each level costs</t>
   </si>
   <si>
-    <t xml:space="preserve">Levels from the medium-lens-film skill (07_quality_levels.md). Hours are Opus agent-hours of building, estimates until the first film is calibrated. Blue cells are inputs.</t>
+    <t xml:space="preserve">Owner rule: level 6 is the minimum for every film. Levels from the medium-lens-film skill (07_quality_levels.md); hours are Opus agent-hours, estimates until ST-01 is calibrated. Blue cells are inputs.</t>
   </si>
   <si>
     <t xml:space="preserve">Level</t>
@@ -1559,16 +1559,16 @@
     <t xml:space="preserve">ST-01 (first story)</t>
   </si>
   <si>
-    <t xml:space="preserve">4 · B mixed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Builds the shared style-deck shaders, the pixel/voxel streamer and kinetic type</t>
+    <t xml:space="preserve">6 · A mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Builds the deck shaders, pixel/voxel streamer, kinetic type, volumetrics and motion blur</t>
   </si>
   <si>
     <t xml:space="preserve">ST-02 … ST-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Reuses the deck shaders; new story, song timing, style picks</t>
+    <t xml:space="preserve">Reuses the deck shaders; new story, sets, hero shot, song timing</t>
   </si>
   <si>
     <t xml:space="preserve">GN-U1A (first A)</t>
@@ -1589,10 +1589,7 @@
     <t xml:space="preserve">GN-U1B (first B)</t>
   </si>
   <si>
-    <t xml:space="preserve">5 · B+ mixed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Builds the streamer room in pixel/voxel</t>
+    <t xml:space="preserve">Builds the streamer room in pixel/voxel at level 6</t>
   </si>
   <si>
     <t xml:space="preserve">GN-U2B … U8B</t>
@@ -6572,23 +6569,23 @@
         <v>1</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="F24" s="5" t="n">
         <f aca="false">D24*E24</f>
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="G24" s="23" t="n">
         <f aca="false">F24*$B$17</f>
-        <v>0.4225</v>
+        <v>0.585</v>
       </c>
       <c r="H24" s="23" t="n">
         <f aca="false">F24*$B$18</f>
-        <v>0.0845</v>
+        <v>0.117</v>
       </c>
       <c r="I24" s="23" t="n">
         <f aca="false">F24*$B$19</f>
-        <v>0.02145</v>
+        <v>0.0297</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>503</v>
@@ -6608,23 +6605,23 @@
         <v>7</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F25" s="5" t="n">
         <f aca="false">D25*E25</f>
-        <v>17.5</v>
+        <v>24.5</v>
       </c>
       <c r="G25" s="23" t="n">
         <f aca="false">F25*$B$17</f>
-        <v>1.1375</v>
+        <v>1.5925</v>
       </c>
       <c r="H25" s="23" t="n">
         <f aca="false">F25*$B$18</f>
-        <v>0.2275</v>
+        <v>0.3185</v>
       </c>
       <c r="I25" s="23" t="n">
         <f aca="false">F25*$B$19</f>
-        <v>0.05775</v>
+        <v>0.08085</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>505</v>
@@ -6710,68 +6707,68 @@
         <v>16</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D28" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28" s="5" t="n">
         <f aca="false">D28*E28</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G28" s="23" t="n">
         <f aca="false">F28*$B$17</f>
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="H28" s="23" t="n">
         <f aca="false">F28*$B$18</f>
-        <v>0.052</v>
+        <v>0.104</v>
       </c>
       <c r="I28" s="23" t="n">
         <f aca="false">F28*$B$19</f>
-        <v>0.0132</v>
+        <v>0.0264</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="D29" s="22" t="n">
         <v>7</v>
       </c>
       <c r="E29" s="22" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F29" s="5" t="n">
         <f aca="false">D29*E29</f>
-        <v>17.5</v>
+        <v>24.5</v>
       </c>
       <c r="G29" s="23" t="n">
         <f aca="false">F29*$B$17</f>
-        <v>1.1375</v>
+        <v>1.5925</v>
       </c>
       <c r="H29" s="23" t="n">
         <f aca="false">F29*$B$18</f>
-        <v>0.2275</v>
+        <v>0.3185</v>
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">F29*$B$19</f>
-        <v>0.05775</v>
+        <v>0.08085</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6782,7 +6779,7 @@
         <v>20</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D30" s="22" t="n">
         <v>1</v>
@@ -6807,7 +6804,7 @@
         <v>0.0396</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6818,7 +6815,7 @@
         <v>20</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D31" s="22" t="n">
         <v>1</v>
@@ -6843,12 +6840,12 @@
         <v>0.0231</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="24"/>
@@ -6859,25 +6856,25 @@
       <c r="E32" s="24"/>
       <c r="F32" s="24" t="n">
         <f aca="false">SUM(F24:F31)</f>
-        <v>98</v>
+        <v>118.5</v>
       </c>
       <c r="G32" s="25" t="n">
         <f aca="false">SUM(G24:G31)</f>
-        <v>6.37</v>
+        <v>7.7025</v>
       </c>
       <c r="H32" s="25" t="n">
         <f aca="false">SUM(H24:H31)</f>
-        <v>1.274</v>
+        <v>1.5405</v>
       </c>
       <c r="I32" s="25" t="n">
         <f aca="false">SUM(I24:I31)</f>
-        <v>0.3234</v>
+        <v>0.39105</v>
       </c>
       <c r="J32" s="24"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -12,16 +12,18 @@
     <sheet name="1 Streamer Stories" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="2 Brand · Generic" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="3 Brand · Master" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Assets" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Style Library" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Effort Levels" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Story &amp; Song" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Assets" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Style Library" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Effort Levels" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'1 Streamer Stories'!$A$4:$U$13</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'2 Brand · Generic'!$A$4:$V$20</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'3 Brand · Master'!$A$9:$I$14</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Assets!$A$4:$I$25</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Style Library'!$A$4:$G$28</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Assets!$A$4:$I$25</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Story &amp; Song'!$A$4:$K$30</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Style Library'!$A$4:$G$28</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="615">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -185,12 +187,12 @@
     <t xml:space="preserve">☐  Style rule: mixed styles from the Style Library tab, no anime/cartoon humans (docs/STYLE_DECK.md)</t>
   </si>
   <si>
+    <t xml:space="preserve">☐  Songs: every film ≥ 45 s; prompts and lyrics in tab Story &amp; Song (docs/SUNO_GUIDE.md)</t>
+  </si>
+  <si>
     <t xml:space="preserve">☐  Product structure decision (one app vs. separate apps) before the Master script</t>
   </si>
   <si>
-    <t xml:space="preserve">☐  All statistics on screen verified at the primary source</t>
-  </si>
-  <si>
     <t xml:space="preserve">Source docs: brand-video/docs/ (SERIES, PIPELINE, USE_CASES, TIER_LIST, CONCEPT). Version 0.1, 2026-10-03.</t>
   </si>
   <si>
@@ -326,7 +328,7 @@
     <t xml:space="preserve">Warm lo-fi indie pop, 120 BPM</t>
   </si>
   <si>
-    <t xml:space="preserve">30 s</t>
+    <t xml:space="preserve">52 s</t>
   </si>
   <si>
     <t xml:space="preserve">Anonymised retelling; ask the author before publishing</t>
@@ -338,21 +340,48 @@
     <t xml:space="preserve">ST-02</t>
   </si>
   <si>
+    <t xml:space="preserve">The raid from the hero (level 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/r/Twitch/comments/1jjlhk4/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found a cowboy-hat speedrunner on YouTube in 2020, started streaming retro games; while playing Ninja Gaiden with 4 viewers, got raided by that same speedrunner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">triumphant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Voxel diorama → CRT/VHS · LED dot-matrix · Kinetic type · Stained glass</t>
   </si>
   <si>
-    <t xml:space="preserve">30–60 s</t>
+    <t xml:space="preserve">Chiptune pop-punk, 140 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anonymised; never name the speedrunner; ask the author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storyline + Suno prompt in tab Story &amp; Song</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engraving → Blueprint · Thermal · Terminal/ASCII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50–60 s</t>
   </si>
   <si>
     <t xml:space="preserve">Pick from the Story Fisher shortlist</t>
   </si>
   <si>
-    <t xml:space="preserve">ST-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engraving → Blueprint · Thermal · Terminal/ASCII</t>
-  </si>
-  <si>
     <t xml:space="preserve">ST-04</t>
   </si>
   <si>
@@ -452,9 +481,6 @@
     <t xml:space="preserve">9:16 first, 16:9</t>
   </si>
   <si>
-    <t xml:space="preserve">30–45 s</t>
-  </si>
-  <si>
     <t xml:space="preserve">GN-U1B</t>
   </si>
   <si>
@@ -464,9 +490,6 @@
     <t xml:space="preserve">B · Music video: song written from the script, pixel/voxel streamer room, kinetic word-synced lyrics. Deck: pixel or voxel → CRT · halftone · kinetic type · neon line</t>
   </si>
   <si>
-    <t xml:space="preserve">20–45 s</t>
-  </si>
-  <si>
     <t xml:space="preserve">GN-U2A</t>
   </si>
   <si>
@@ -813,6 +836,550 @@
   </si>
   <si>
     <t xml:space="preserve">End card, sonic logo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Story &amp; Song · storyline, Suno prompt and lyrics per film</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paste 'Suno · Style' into Style of Music, 'Suno · Exclude' into Exclude, 'Lyrics' into Lyrics (Custom mode, v5.5, Duration slider = Length). Every film is at least 45 s. Guide: docs/SUNO_GUIDE.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Storyline (what the viewer sees)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suno · Style</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suno · Exclude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyrics (with Suno tags) / statements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Song status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The train ride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel city at Christmas: a streamer who usually plays games at a desk steps outside, phone up, LIVE. Viewer counter climbs 1, 2, 3. On the evening train, rain streaks the window and the city slides past (hero shot). The signal bars fall, the picture freezes: signal lost. Black. The chat appears big, typed word by word: 'that was amazing. thank you'. Front-page halftone burst: 3 VIEWERS. ENOUGH. Back on the platform the streamer stops and reads it. The city turns warm; a small spark appears next to the message (companion cameo). End card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warm lo-fi indie pop, gentle and hopeful, glockenspiel and felt piano, soft synth pads, brushed train-rhythm percussion, soft clear vocal up front, intimate dry production, 120 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heavy reverb, autotune, rap verses, spoken word intro, long instrumental intro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: glockenspiel, train rhythm]
+[Verse: soft vocal]
+Took the stream outside on Christmas night
+Phone in my cold hand, city lights
+Three people watching, that's my crowd
+Talking to the street out loud
+Evening train, the windows run
+Rain on the glass, still on, still on
+[Pre-Chorus: almost spoken]
+Signal fading
+[Break]
+[Chorus: warm, fuller]
+You stayed till the signal died
+Said it was amazing, on a train at night
+Three is not nothing, three is enough
+Somebody was there, that's what it was
+[Outro: soft]
+That's why I do this
+That's why I do this
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facts from the post only. Script: docs/scripts/ST-01_train-ride.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The raid from the hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voxel diorama: 2020, a YouTube video on an old monitor shows a speedrunner in a cowboy hat (voxel, no face). The viewer makes a Twitch account that night and starts streaming retro games. CRT look: Ninja Gaiden-style pixel action, counter at 4 viewers. LED dot-matrix alert: RAID. It is the same speedrunner. The chat floods (kinetic type), stained-glass burst on the chorus, voxel room fills with lights. End card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chiptune pop-punk, triumphant and fast, 8-bit synth leads with live drums and driving bass, bright clear vocal, punchy modern production, 140 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: 8-bit lead]
+[Verse]
+Twenty-twenty, found a video
+Cowboy hat and a speedrun
+Made an account that very night
+Started streaming the old games
+[Pre-Chorus: building]
+Four people watching, Ninja Gaiden on
+[Break]
+[Chorus: full band, shout-along]
+Then the raid came in, it was him
+The one who started all of this
+Look who's in my chat tonight
+Look who's watching now
+[Outro]
+Look who's watching now
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facts from the post (Story Fisher, quality 9). Never name the speedrunner. Check the full post before scripting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(pick from the Story Fisher shortlist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written after the story is chosen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A · majestic technical (instrumental)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A single 'hi' as a point of light drifting into a vast dark space of chat; it fades, unseen. The companion's spark rises, catches it, and the reply lights a path. More hellos arrive; each is caught. They form a constellation of welcomed names.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cinematic orchestral electronic, majestic and hopeful, felt piano motif, warm strings, deep sub swells, pristine production, 90 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vocals, choir words, EDM drop, dubstep, long fade-out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental ON. Lyrics field (structure only):
+[Intro: solo motif]
+[Build: layers enter]
+[Swell]
+[Climax: full]
+[Outro: motif returns]
+[End]
+On-screen statements (not sung):
+Every hello matters.
+Most go unanswered.
+Not anymore.
+Chobbot greets every first-time chatter. (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statements shown as text, timed to the swells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B · music video (song)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel streamer mid boss fight. A new name types 'hi'; it scrolls away unseen, a timer counts 0:01…0:40, the name leaves. Rewind on the break: same moment with the companion. The spark answers 'hey Sam, first time? welcome in' and flags the streamer, who waves. A week later Sam types 'back again'; the bot: 'welcome back, Sam'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upbeat synth-pop, playful and bright, plucky synths and handclaps, punchy drums, clear bright vocal, clean modern production, 124 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: plucky synth]
+[Verse]
+Boss fight, eyes on the screen
+Someone typed hi in between
+Scrolled away, nobody saw
+Forty seconds, then they're gone
+[Pre-Chorus: half-spoken]
+What if someone said hi back
+[Break]
+[Chorus: full]
+Hey, welcome in, first time here?
+Somebody answered, loud and clear
+Nobody slips through the chat
+A week later, Sam comes back
+[Outro]
+Welcome back
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lyrics appear as on-screen text; nobody sings on screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identical questions fall as glyphs and form a storm. The companion turns the storm into one ordered column of answers, and the space goes quiet and clear around a single focused point of play.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cinematic minimal electronic, focused and precise, pulsing arpeggio, glassy pads, ticking percussion, clean build, 100 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental ON. Lyrics field (structure only):
+[Intro: solo motif]
+[Build: layers enter]
+[Swell]
+[Climax: full]
+[Outro: motif returns]
+[End]
+On-screen statements (not sung):
+The same question. Forty times.
+Answered once. Remembered.
+Your focus stays on the game. (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The same question pours in as pixel cards that stack up on the desk. The streamer turns to answer and dies in game. Rewind: the companion answers each card instantly; the cards fold into one neat FAQ stack; the streamer clutches the round.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">funky electro-pop, cheeky and energetic, slap bass and chopped synth hooks, crisp drums, bright clear vocal, tight production, 118 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: slap bass]
+[Verse]
+What's your rank, what's your rig
+What's the song, what's your sens
+Fortieth time tonight
+Turn to answer, lose the fight
+[Pre-Chorus]
+Same question, again, again
+[Break]
+[Chorus: full]
+Let the bot take that one
+Answer once and it's done
+Eyes on the game, clutch the round
+Chat still heard, every sound
+[Outro]
+Clutch the round
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A storm of red particles crashes against a small sphere of light around a lone desk at night. The companion's shield lights up cell by cell; the storm breaks around it and passes. Dawn rises over a calm city.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dark cinematic hybrid orchestral, tense then triumphant, low brass and taiko pulses, rising strings, resolves to bright major, 95 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental ON. Lyrics field (structure only):
+[Intro: solo motif]
+[Build: layers enter]
+[Swell]
+[Climax: full]
+[Outro: motif returns]
+[End]
+On-screen statements (not sung):
+Raids come at 2 AM.
+No mod online.
+Protection that stays on. (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Night stream, mods asleep. Red spam floods the chat; on every snare it cracks the monitor glass (glitch). The streamer freezes. Break. The companion's shield: the noise is filtered in a second and dissolves; calm returns; in the morning a clean log waits for the mods.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dark synthwave turning bright, tense then relieved, distorted bass and gated snare, opening into warm major chords, clear vocal, 128 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: low pulse]
+[Verse: tense]
+Two a.m., the mods asleep
+Chat goes red, a hundred deep
+Same words, a hundred names
+Hands off the keys, I freeze
+[Pre-Chorus: whispered]
+Who's on watch at two a.m.
+[Break]
+[Chorus: bright, major]
+Filtered in a second flat
+Calm comes back into the chat
+Logged it all for the morning crew
+Stream goes on, we got you
+[Outro]
+Stream goes on
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The viewer curve as a vast terrain seen from above at night. The camera glides to a canyon at 1:12. A scanning light from the report sweeps the canyon and reveals what lies beneath: the moment that caused it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cinematic ambient electronic, investigative then awe, deep pads and pulsing low synth, piano motif, rising build, 85 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental ON. Lyrics field (structure only):
+[Intro: solo motif]
+[Build: layers enter]
+[Swell]
+[Climax: full]
+[Outro: motif returns]
+[End]
+On-screen statements (not sung):
+Numbers say what. Not why.
+Insights shows why. (confirm)
+Every drop, explained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The viewer graph is a pixel mountain range; at 1:12 a cliff. The streamer stares, no idea why. The report overlays stream and chat on the graph: a nine-minute loading screen and a silent chat line up exactly with the drop. Next stream, the line holds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chill electronic pop, curious then confident, ticking hi-hats and warm bass, soft synth chords, clean bright vocal, 115 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: ticking hats]
+[Verse]
+One hour twelve, the line goes down
+Half the room just left the town
+Was it me, the game, the time
+Scrolling numbers, no reply
+[Pre-Chorus]
+What happened at one twelve
+[Break]
+[Chorus: full]
+Nine minutes of a loading screen
+Chat went quiet in between
+Now I see it, now I know
+Next stream, the line holds
+[Outro]
+Now I know
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A river of footage flows through the dark. Four bright points rise out of it, slowly, and hang in the air as a small constellation: the four moments that matter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cinematic neo-classical electronic, calm and grand, felt piano and cello, shimmering arpeggios, slow swell, 80 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental ON. Lyrics field (structure only):
+[Intro: solo motif]
+[Build: layers enter]
+[Swell]
+[Climax: full]
+[Outro: motif returns]
+[End]
+On-screen statements (not sung):
+Four hours of stream.
+Four moments that matter.
+Found while you rest. (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midnight. The VOD timeline stretches like an endless road; the streamer scrubs, half asleep. The companion lifts four glowing moments out of the chat spikes; the clips are ready when the stream ends. Laptop closes. Sleep.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dreamy bedroom pop, tired then relieved, lo-fi drums and warm Rhodes, soft clear vocal, gentle lift in the chorus, 110 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: warm Rhodes]
+[Verse: sleepy]
+Stream is over, midnight now
+Four hours of footage, scrub it down
+Where was the moment, where was the laugh
+Rewind, rewind, half asleep
+[Pre-Chorus]
+There's got to be a faster way
+[Break]
+[Chorus: lift]
+Chat spiked here, and here, and here
+Four best moments, already clear
+Clips are ready, go to sleep
+The best of tonight is yours to keep
+[Outro]
+Go to sleep
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An ocean of data points. A single question rises from the streamer as a beam of light; the data reorganises around it into three clear paths.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cinematic electronic, majestic and clear, evolving pads and piano, tight pulse, big resolving chord, 92 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental ON. Lyrics field (structure only):
+[Intro: solo motif]
+[Build: layers enter]
+[Swell]
+[Climax: full]
+[Outro: motif returns]
+[End]
+On-screen statements (not sung):
+You have the data.
+Now ask it anything.
+Answers, not charts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The streamer faces a wall of charts (data UI style); the numbers blur. They type a question to the analyst bot. Three plain answers appear as cards. Next week the graph climbs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upbeat indie electronic, curious then confident, bright synth plucks and tight drums, warm bass, clear vocal, 122 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: synth plucks]
+[Verse]
+Charts on charts, lines on lines
+Followers, minutes, peaks and times
+All these numbers, what do they mean
+Staring at a glowing screen
+[Pre-Chorus: spoken]
+So what should I change?
+[Break]
+[Chorus: full]
+Three things, plain and clear
+Start at eight, your people are here
+Shorter breaks, say hi by name
+Next week, it's not the same
+[Outro]
+Ask me anything
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months pass as seasons over a single lit window. Each stream leaves a point of light around the streamer; slowly they join into a constellation: the second brain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cinematic orchestral, emotional and majestic, piano motif and warm strings, choir pad, slow build to a glowing finale, 84 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental ON. Lyrics field (structure only):
+[Intro: solo motif]
+[Build: layers enter]
+[Swell]
+[Climax: full]
+[Outro: motif returns]
+[End]
+On-screen statements (not sung):
+Every stream starts from zero.
+Unless something remembers.
+A companion that grows with you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anniversary stream. A regular types an inside joke from a year ago; the streamer has forgotten it. The companion recalls the moment and plays it back as a memory card; chat erupts. The memory ring around the companion glows with a year of moments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nostalgic indie pop, warm and joyful, jangly guitars and glockenspiel, handclaps, clear warm vocal, gang vocals in the chorus, 116 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: jangly guitar]
+[Verse]
+A year ago a joke was born
+Chat still knows it, every one
+I forgot, the nights move on
+Every stream from zero again
+[Pre-Chorus]
+Who remembers when
+[Break]
+[Chorus: gang vocals]
+It remembers every name
+Every joke and every game
+One year later, it's still here
+Brings it back, the whole chat cheers
+[Outro]
+It remembers
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scattered numbers swirl and condense into one elegant document of light, which folds into a paper plane and flies toward a bright horizon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cinematic modern orchestral, confident and elegant, staccato strings and piano, clean pulse, bright resolving finale, 96 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental ON. Lyrics field (structure only):
+[Intro: solo motif]
+[Build: layers enter]
+[Swell]
+[Climax: full]
+[Outro: motif returns]
+[End]
+On-screen statements (not sung):
+Sponsors want proof.
+One report. Every number. (confirm)
+Sent before the weekend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friday: an email, 'report by Friday?'. The streamer is buried in a voxel tower of spreadsheets. The companion builds one clean report card; send. Weekend lights come on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">funky disco-pop, stressed then celebratory, four-on-the-floor and funky guitar, brass stabs, clear vocal, 120 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: funky guitar]
+[Verse]
+Email says by Friday, please
+Numbers from the last three weeks
+Spreadsheet cells, copy, paste
+Weekend going down the drain
+[Pre-Chorus]
+There goes Saturday
+[Break]
+[Chorus: full, brass]
+One report, ready to send
+Every number, start to end
+Hit send, it's Friday night
+Weekend's back, it's all right
+[Outro]
+Hit send
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master · A new era</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75–90 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Alone: one streamer, one screen in the dark; pull back through the window to a city, then a planet of lit windows. 2 The spark: one window turns warm; the companion is born. 3 The architecture: flythrough of the system, live chat → stream data → reports → memory. 4 The second brain: the memory ring grows into a constellation around the streamer. 5 A new era: window after window lights warm; the logo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cinematic hybrid orchestral electronic, majestic and awe-inspiring, solo felt piano motif, expanding strings, deep sub and choir pad, builds to a vast final hit, pristine production, 90 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrumental ON. Lyrics field (structure only):
+[Intro: solo felt piano]
+[Build: strings enter, low pulse]
+[Movement: arpeggios, rising]
+[Swell: choir pad]
+[Climax: full orchestra and synths]
+[Outro: piano motif returns]
+[End]
+On-screen statements (not sung):
+Every night, millions create alone.
+Until now.
+It listens. It learns. It remembers.
+Not a tool. A second brain.
+A companion for every creator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five movements, statements timed to the swells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master · Never live alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same five movements as A, told through one streamer over months: empty room → the first hello from the companion → after-stream reports → the memory ring growing with names and jokes → the city of warm windows. Mixed style deck, voxel/pixel streamer, kinetic lyrics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anthemic indie pop with cinematic strings, hopeful and uplifting, piano and pulsing synth bass, big drums in the chorus, clear emotive vocal, gang vocals in the final chorus, 118 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: piano]
+[Verse 1]
+Every night, another window glows
+Someone streaming to an empty room
+Says hello to no one there
+Talks until the chat comes through
+[Pre-Chorus]
+Then a little light said hi
+[Break]
+[Chorus]
+Never live alone
+Somebody's there when you go on
+Remembers every name
+Grows with you, stream by stream
+[Verse 2]
+After the stream it counts the night
+Finds the moments, shows you why
+Months go by, the ring grows wide
+Every story kept inside
+[Final Chorus: gang vocals]
+Never live alone
+Somebody's there when you go on
+Remembers every name
+Grows with you, stream by stream
+[Outro]
+Never live alone
+[End]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Never live alone' is a placeholder tagline until you decide</t>
   </si>
   <si>
     <t xml:space="preserve">Shared assets</t>
@@ -2065,6 +2632,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFEEEEEE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFD5F2DC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -2074,14 +2649,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8D3D3"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEEEEEE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2141,7 +2708,7 @@
       <rgbColor rgb="FF2BB673"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC2410C"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1F2430"/>
@@ -2167,6 +2734,10 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -2879,27 +3450,43 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
+      <c r="B7" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>82</v>
+      </c>
       <c r="H7" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="I7" s="18"/>
+        <v>106</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>107</v>
+      </c>
       <c r="J7" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="L7" s="18"/>
+        <v>108</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>109</v>
+      </c>
       <c r="M7" s="5" t="s">
         <v>38</v>
       </c>
@@ -2916,15 +3503,17 @@
         <v>38</v>
       </c>
       <c r="R7" s="18"/>
-      <c r="S7" s="5"/>
+      <c r="S7" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="T7" s="18"/>
       <c r="U7" s="18" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -2933,14 +3522,14 @@
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
       <c r="H8" s="5" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="L8" s="18"/>
       <c r="M8" s="5" t="s">
@@ -2962,12 +3551,12 @@
       <c r="S8" s="5"/>
       <c r="T8" s="18"/>
       <c r="U8" s="18" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -2976,14 +3565,14 @@
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
       <c r="H9" s="5" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="L9" s="18"/>
       <c r="M9" s="5" t="s">
@@ -3005,12 +3594,12 @@
       <c r="S9" s="5"/>
       <c r="T9" s="18"/>
       <c r="U9" s="18" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -3019,14 +3608,14 @@
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
       <c r="H10" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I10" s="18"/>
       <c r="J10" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="L10" s="18"/>
       <c r="M10" s="5" t="s">
@@ -3048,12 +3637,12 @@
       <c r="S10" s="5"/>
       <c r="T10" s="18"/>
       <c r="U10" s="18" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -3062,14 +3651,14 @@
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="5" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="L11" s="18"/>
       <c r="M11" s="5" t="s">
@@ -3091,12 +3680,12 @@
       <c r="S11" s="5"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -3105,14 +3694,14 @@
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="5" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="5" t="s">
@@ -3134,12 +3723,12 @@
       <c r="S12" s="5"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -3148,14 +3737,14 @@
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
       <c r="H13" s="5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="5" t="s">
         <v>85</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="L13" s="18"/>
       <c r="M13" s="5" t="s">
@@ -3177,7 +3766,7 @@
       <c r="S13" s="5"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3346,12 +3935,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3359,37 +3948,37 @@
         <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>64</v>
@@ -3424,44 +4013,44 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K5" s="18"/>
       <c r="L5" s="5" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>38</v>
@@ -3484,44 +4073,44 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K6" s="18"/>
       <c r="L6" s="5" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>38</v>
@@ -3544,44 +4133,44 @@
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="K7" s="18"/>
       <c r="L7" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>38</v>
@@ -3604,44 +4193,44 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>145</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="5" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>38</v>
@@ -3664,44 +4253,44 @@
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K9" s="18"/>
       <c r="L9" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>38</v>
@@ -3724,44 +4313,44 @@
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>154</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K10" s="18"/>
       <c r="L10" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>38</v>
@@ -3784,44 +4373,44 @@
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K11" s="18"/>
       <c r="L11" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>38</v>
@@ -3844,44 +4433,44 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>163</v>
-      </c>
       <c r="D12" s="5" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K12" s="18"/>
       <c r="L12" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>38</v>
@@ -3904,44 +4493,44 @@
     </row>
     <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="J13" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K13" s="18"/>
       <c r="L13" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>38</v>
@@ -3964,44 +4553,44 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>172</v>
-      </c>
       <c r="D14" s="5" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F14" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="J14" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K14" s="18"/>
       <c r="L14" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="O14" s="5" t="s">
         <v>38</v>
@@ -4024,44 +4613,44 @@
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K15" s="18"/>
       <c r="L15" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>38</v>
@@ -4084,44 +4673,44 @@
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="D16" s="5" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K16" s="18"/>
       <c r="L16" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>38</v>
@@ -4144,44 +4733,44 @@
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K17" s="18"/>
       <c r="L17" s="5" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>38</v>
@@ -4204,44 +4793,44 @@
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>191</v>
-      </c>
       <c r="E18" s="5" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="5" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="O18" s="5" t="s">
         <v>38</v>
@@ -4264,44 +4853,44 @@
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="5" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>38</v>
@@ -4324,44 +4913,44 @@
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="D20" s="5" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="K20" s="18"/>
       <c r="L20" s="5" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="O20" s="5" t="s">
         <v>38</v>
@@ -4543,12 +5132,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4556,13 +5145,13 @@
         <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>65</v>
@@ -4571,7 +5160,7 @@
         <v>64</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>67</v>
@@ -4600,25 +5189,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>38</v>
@@ -4638,30 +5227,30 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="18" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>38</v>
@@ -4681,38 +5270,38 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="18" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>75</v>
@@ -4723,22 +5312,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>38</v>
@@ -4750,22 +5339,22 @@
         <v>2</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>38</v>
@@ -4777,22 +5366,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>38</v>
@@ -4804,22 +5393,22 @@
         <v>4</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>38</v>
@@ -4831,22 +5420,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>38</v>
@@ -5015,6 +5604,942 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFC2410C"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="337.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:K30"/>
+  <conditionalFormatting sqref="J5:J30">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>J5="Not started"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>J5="In progress"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>J5="Review"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>J5="Approved"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>J5="Blocked"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>J5="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J30" type="list">
+      <formula1>"Not started,In progress,Review,Approved,Blocked,N/A"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FF5B6170"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -5034,38 +6559,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>261</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>262</v>
+        <v>356</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>263</v>
+        <v>357</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>265</v>
+        <v>359</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>266</v>
+        <v>360</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>74</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>267</v>
+        <v>361</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>75</v>
@@ -5073,19 +6598,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>268</v>
+        <v>362</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>38</v>
@@ -5093,24 +6618,24 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18" t="s">
-        <v>272</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>274</v>
+        <v>368</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>38</v>
@@ -5121,16 +6646,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>275</v>
+        <v>369</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
@@ -5142,19 +6667,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>277</v>
+        <v>371</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>279</v>
+        <v>373</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>38</v>
@@ -5162,21 +6687,21 @@
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
       <c r="I8" s="18" t="s">
-        <v>280</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>281</v>
+        <v>375</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>282</v>
+        <v>376</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
@@ -5185,24 +6710,24 @@
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18" t="s">
-        <v>283</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>284</v>
+        <v>378</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>285</v>
+        <v>379</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>286</v>
+        <v>380</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>38</v>
@@ -5210,24 +6735,24 @@
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18" t="s">
-        <v>287</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>288</v>
+        <v>382</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>285</v>
+        <v>379</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>289</v>
+        <v>383</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>290</v>
+        <v>384</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>38</v>
@@ -5235,24 +6760,24 @@
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>291</v>
+        <v>385</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>285</v>
+        <v>379</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>289</v>
+        <v>383</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>292</v>
+        <v>386</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>38</v>
@@ -5260,21 +6785,21 @@
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18" t="s">
-        <v>293</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>294</v>
+        <v>388</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>285</v>
+        <v>379</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>289</v>
+        <v>383</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
@@ -5283,21 +6808,21 @@
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18" t="s">
-        <v>295</v>
+        <v>389</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>296</v>
+        <v>390</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>285</v>
+        <v>379</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>297</v>
+        <v>391</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>298</v>
+        <v>392</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
@@ -5306,21 +6831,21 @@
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18" t="s">
-        <v>299</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>300</v>
+        <v>394</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>301</v>
+        <v>395</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>302</v>
+        <v>396</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
@@ -5329,21 +6854,21 @@
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18" t="s">
-        <v>303</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>304</v>
+        <v>398</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>305</v>
+        <v>399</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>306</v>
+        <v>400</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
@@ -5352,21 +6877,21 @@
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18" t="s">
-        <v>307</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>308</v>
+        <v>402</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>305</v>
+        <v>399</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>309</v>
+        <v>403</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
@@ -5375,24 +6900,24 @@
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18" t="s">
-        <v>310</v>
+        <v>404</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>311</v>
+        <v>405</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>305</v>
+        <v>399</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>309</v>
+        <v>403</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>312</v>
+        <v>406</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>38</v>
@@ -5400,24 +6925,24 @@
       <c r="G18" s="18"/>
       <c r="H18" s="18"/>
       <c r="I18" s="18" t="s">
-        <v>313</v>
+        <v>407</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>314</v>
+        <v>408</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>315</v>
+        <v>409</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>278</v>
+        <v>372</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>286</v>
+        <v>380</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>38</v>
@@ -5425,24 +6950,24 @@
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18" t="s">
-        <v>316</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>317</v>
+        <v>411</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>315</v>
+        <v>409</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>289</v>
+        <v>383</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>318</v>
+        <v>412</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>38</v>
@@ -5453,19 +6978,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>319</v>
+        <v>413</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>320</v>
+        <v>414</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>321</v>
+        <v>415</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>322</v>
+        <v>416</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>323</v>
+        <v>417</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>39</v>
@@ -5473,24 +6998,24 @@
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18" t="s">
-        <v>324</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>325</v>
+        <v>419</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>326</v>
+        <v>420</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>327</v>
+        <v>421</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>38</v>
@@ -5498,24 +7023,24 @@
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>329</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>330</v>
+        <v>424</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>309</v>
+        <v>403</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>327</v>
+        <v>421</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>38</v>
@@ -5523,24 +7048,24 @@
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18" t="s">
-        <v>331</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>332</v>
+        <v>426</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>309</v>
+        <v>403</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>333</v>
+        <v>427</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>328</v>
+        <v>422</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>38</v>
@@ -5548,21 +7073,21 @@
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18" t="s">
-        <v>334</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>335</v>
+        <v>429</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>336</v>
+        <v>430</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>337</v>
+        <v>431</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>338</v>
+        <v>432</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
@@ -5571,7 +7096,7 @@
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18" t="s">
-        <v>339</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -5613,7 +7138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF2BB673"/>
@@ -5633,32 +7158,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>341</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>342</v>
+        <v>436</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>343</v>
+        <v>437</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>344</v>
+        <v>438</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>345</v>
+        <v>439</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>346</v>
+        <v>440</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>347</v>
+        <v>441</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>75</v>
@@ -5666,65 +7191,65 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>348</v>
+        <v>442</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>350</v>
+        <v>444</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>351</v>
+        <v>445</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>352</v>
+        <v>446</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>353</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>354</v>
+        <v>448</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>355</v>
+        <v>449</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>356</v>
+        <v>450</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>352</v>
+        <v>446</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>357</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>358</v>
+        <v>452</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>359</v>
+        <v>453</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>360</v>
+        <v>454</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>361</v>
+        <v>455</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>38</v>
@@ -5733,19 +7258,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>362</v>
+        <v>456</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>363</v>
+        <v>457</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>364</v>
+        <v>458</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>365</v>
+        <v>459</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>38</v>
@@ -5754,19 +7279,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>366</v>
+        <v>460</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>367</v>
+        <v>461</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>368</v>
+        <v>462</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>369</v>
+        <v>463</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>38</v>
@@ -5775,19 +7300,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>370</v>
+        <v>464</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>371</v>
+        <v>465</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>372</v>
+        <v>466</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>373</v>
+        <v>467</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>38</v>
@@ -5796,42 +7321,42 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>374</v>
+        <v>468</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>375</v>
+        <v>469</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>376</v>
+        <v>470</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>373</v>
+        <v>467</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>377</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>378</v>
+        <v>472</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>379</v>
+        <v>473</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>380</v>
+        <v>474</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>365</v>
+        <v>459</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>38</v>
@@ -5840,19 +7365,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>381</v>
+        <v>475</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>382</v>
+        <v>476</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>383</v>
+        <v>477</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>369</v>
+        <v>463</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>38</v>
@@ -5861,19 +7386,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>384</v>
+        <v>478</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>385</v>
+        <v>479</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>386</v>
+        <v>480</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>387</v>
+        <v>481</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>38</v>
@@ -5882,19 +7407,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>388</v>
+        <v>482</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>389</v>
+        <v>483</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>386</v>
+        <v>480</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>369</v>
+        <v>463</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>38</v>
@@ -5903,19 +7428,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>390</v>
+        <v>484</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>391</v>
+        <v>485</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>372</v>
+        <v>466</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>361</v>
+        <v>455</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>38</v>
@@ -5924,19 +7449,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>392</v>
+        <v>486</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>393</v>
+        <v>487</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>376</v>
+        <v>470</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>394</v>
+        <v>488</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>38</v>
@@ -5945,65 +7470,65 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>395</v>
+        <v>489</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>396</v>
+        <v>490</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>397</v>
+        <v>491</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>352</v>
+        <v>446</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>398</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>399</v>
+        <v>493</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>400</v>
+        <v>494</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>401</v>
+        <v>495</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>352</v>
+        <v>446</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>402</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>403</v>
+        <v>497</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>404</v>
+        <v>498</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>405</v>
+        <v>499</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>373</v>
+        <v>467</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>38</v>
@@ -6012,42 +7537,42 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>406</v>
+        <v>500</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>349</v>
+        <v>443</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>407</v>
+        <v>501</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>408</v>
+        <v>502</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>409</v>
+        <v>503</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>410</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>411</v>
+        <v>505</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>412</v>
+        <v>506</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>413</v>
+        <v>507</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>414</v>
+        <v>508</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>415</v>
+        <v>509</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>38</v>
@@ -6056,19 +7581,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>416</v>
+        <v>510</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>412</v>
+        <v>506</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>417</v>
+        <v>511</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>414</v>
+        <v>508</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>415</v>
+        <v>509</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>38</v>
@@ -6077,19 +7602,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>418</v>
+        <v>512</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>412</v>
+        <v>506</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>419</v>
+        <v>513</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>414</v>
+        <v>508</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>420</v>
+        <v>514</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>38</v>
@@ -6098,19 +7623,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>421</v>
+        <v>515</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>412</v>
+        <v>506</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>422</v>
+        <v>516</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>423</v>
+        <v>517</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>415</v>
+        <v>509</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>38</v>
@@ -6119,19 +7644,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>424</v>
+        <v>518</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>412</v>
+        <v>506</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>425</v>
+        <v>519</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>426</v>
+        <v>520</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>420</v>
+        <v>514</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>38</v>
@@ -6140,48 +7665,48 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>427</v>
+        <v>521</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>428</v>
+        <v>522</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>429</v>
+        <v>523</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>429</v>
+        <v>523</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>429</v>
+        <v>523</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>430</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>431</v>
+        <v>525</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>428</v>
+        <v>522</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>429</v>
+        <v>523</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>429</v>
+        <v>523</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>429</v>
+        <v>523</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>432</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -6234,7 +7759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF0F6FDE"/>
@@ -6256,32 +7781,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>433</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>434</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>435</v>
+        <v>529</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>436</v>
+        <v>530</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>437</v>
+        <v>531</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>438</v>
+        <v>532</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>440</v>
+        <v>534</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6289,19 +7814,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>441</v>
+        <v>535</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>442</v>
+        <v>536</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>443</v>
+        <v>537</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>444</v>
+        <v>538</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>445</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6309,19 +7834,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>446</v>
+        <v>540</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>447</v>
+        <v>541</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>448</v>
+        <v>542</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>449</v>
+        <v>543</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>450</v>
+        <v>544</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6329,19 +7854,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>451</v>
+        <v>545</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>452</v>
+        <v>546</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>453</v>
+        <v>547</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>454</v>
+        <v>548</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>455</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6349,19 +7874,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>456</v>
+        <v>550</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6369,19 +7894,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6389,19 +7914,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>464</v>
+        <v>558</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>465</v>
+        <v>559</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>466</v>
+        <v>560</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>467</v>
+        <v>561</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6409,19 +7934,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>468</v>
+        <v>562</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>469</v>
+        <v>563</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>470</v>
+        <v>564</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>471</v>
+        <v>565</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>472</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6429,19 +7954,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>473</v>
+        <v>567</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>474</v>
+        <v>568</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>475</v>
+        <v>569</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>476</v>
+        <v>570</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>472</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6449,19 +7974,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>477</v>
+        <v>571</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>478</v>
+        <v>572</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>479</v>
+        <v>573</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>480</v>
+        <v>574</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>481</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6469,29 +7994,29 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>482</v>
+        <v>576</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>483</v>
+        <v>577</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>484</v>
+        <v>578</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>485</v>
+        <v>579</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>486</v>
+        <v>580</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>487</v>
+        <v>581</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>488</v>
+        <v>582</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>0.065</v>
@@ -6499,7 +8024,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>489</v>
+        <v>583</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>0.013</v>
@@ -6507,7 +8032,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>490</v>
+        <v>584</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>0.0033</v>
@@ -6515,55 +8040,55 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>491</v>
+        <v>585</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>492</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>493</v>
+        <v>587</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>435</v>
+        <v>529</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>494</v>
+        <v>588</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>495</v>
+        <v>589</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>496</v>
+        <v>590</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>497</v>
+        <v>591</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>498</v>
+        <v>592</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>499</v>
+        <v>593</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>500</v>
+        <v>594</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>501</v>
+        <v>595</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>502</v>
+        <v>596</v>
       </c>
       <c r="D24" s="22" t="n">
         <v>1</v>
@@ -6588,18 +8113,18 @@
         <v>0.0297</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>503</v>
+        <v>597</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>504</v>
+        <v>598</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>502</v>
+        <v>596</v>
       </c>
       <c r="D25" s="22" t="n">
         <v>7</v>
@@ -6624,18 +8149,18 @@
         <v>0.08085</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>505</v>
+        <v>599</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>506</v>
+        <v>600</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>507</v>
+        <v>601</v>
       </c>
       <c r="D26" s="22" t="n">
         <v>1</v>
@@ -6660,18 +8185,18 @@
         <v>0.0297</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>508</v>
+        <v>602</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>509</v>
+        <v>603</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>507</v>
+        <v>601</v>
       </c>
       <c r="D27" s="22" t="n">
         <v>7</v>
@@ -6696,18 +8221,18 @@
         <v>0.08085</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>510</v>
+        <v>604</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>511</v>
+        <v>605</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>502</v>
+        <v>596</v>
       </c>
       <c r="D28" s="22" t="n">
         <v>1</v>
@@ -6732,18 +8257,18 @@
         <v>0.0264</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>512</v>
+        <v>606</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>513</v>
+        <v>607</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>502</v>
+        <v>596</v>
       </c>
       <c r="D29" s="22" t="n">
         <v>7</v>
@@ -6768,18 +8293,18 @@
         <v>0.08085</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>514</v>
+        <v>608</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>515</v>
+        <v>609</v>
       </c>
       <c r="D30" s="22" t="n">
         <v>1</v>
@@ -6804,18 +8329,18 @@
         <v>0.0396</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>516</v>
+        <v>610</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>517</v>
+        <v>611</v>
       </c>
       <c r="D31" s="22" t="n">
         <v>1</v>
@@ -6840,12 +8365,12 @@
         <v>0.0231</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>518</v>
+        <v>612</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="24" t="s">
-        <v>519</v>
+        <v>613</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="24"/>
@@ -6874,7 +8399,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>520</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="618">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -190,12 +190,15 @@
     <t xml:space="preserve">☐  Songs: every film ≥ 45 s; prompts and lyrics in tab Story &amp; Song (docs/SUNO_GUIDE.md)</t>
   </si>
   <si>
-    <t xml:space="preserve">☐  Product structure decision (one app vs. separate apps) before the Master script</t>
+    <t xml:space="preserve">☐  Every Story opens with “Based on a true story” (1.5 bars, 2.5–3 s, over the first shot)</t>
   </si>
   <si>
     <t xml:space="preserve">Source docs: brand-video/docs/ (SERIES, PIPELINE, USE_CASES, TIER_LIST, CONCEPT). Version 0.1, 2026-10-03.</t>
   </si>
   <si>
+    <t xml:space="preserve">☐  All statistics on screen verified at the primary source</t>
+  </si>
+  <si>
     <t xml:space="preserve">Section 1 · Streamer Stories (music videos)</t>
   </si>
   <si>
@@ -871,7 +874,7 @@
     <t xml:space="preserve">MV</t>
   </si>
   <si>
-    <t xml:space="preserve">Pixel city at Christmas: a streamer who usually plays games at a desk steps outside, phone up, LIVE. Viewer counter climbs 1, 2, 3. On the evening train, rain streaks the window and the city slides past (hero shot). The signal bars fall, the picture freezes: signal lost. Black. The chat appears big, typed word by word: 'that was amazing. thank you'. Front-page halftone burst: 3 VIEWERS. ENOUGH. Back on the platform the streamer stops and reads it. The city turns warm; a small spark appears next to the message (companion cameo). End card.</t>
+    <t xml:space="preserve">0:00–0:03 “Based on a true story” over a slow push into the pixel city (out on the beat). Then: Pixel city at Christmas: a streamer who usually plays games at a desk steps outside, phone up, LIVE. Viewer counter climbs 1, 2, 3. On the evening train, rain streaks the window and the city slides past (hero shot). The signal bars fall, the picture freezes: signal lost. Black. The chat appears big, typed word by word: 'that was amazing. thank you'. Front-page halftone burst: 3 VIEWERS. ENOUGH. Back on the platform the streamer stops and reads it. The city turns warm; a small spark appears next to the message (companion cameo). End card + credit: Story shared by a streamer on Reddit.</t>
   </si>
   <si>
     <t xml:space="preserve">warm lo-fi indie pop, gentle and hopeful, glockenspiel and felt piano, soft synth pads, brushed train-rhythm percussion, soft clear vocal up front, intimate dry production, 120 BPM</t>
@@ -880,7 +883,7 @@
     <t xml:space="preserve">heavy reverb, autotune, rap verses, spoken word intro, long instrumental intro</t>
   </si>
   <si>
-    <t xml:space="preserve">[Intro: glockenspiel, train rhythm]
+    <t xml:space="preserve">[Intro: 2 bars, instrumental, glockenspiel, train rhythm]
 [Verse: soft vocal]
 Took the stream outside on Christmas night
 Phone in my cold hand, city lights
@@ -908,13 +911,13 @@
     <t xml:space="preserve">The raid from the hero</t>
   </si>
   <si>
-    <t xml:space="preserve">Voxel diorama: 2020, a YouTube video on an old monitor shows a speedrunner in a cowboy hat (voxel, no face). The viewer makes a Twitch account that night and starts streaming retro games. CRT look: Ninja Gaiden-style pixel action, counter at 4 viewers. LED dot-matrix alert: RAID. It is the same speedrunner. The chat floods (kinetic type), stained-glass burst on the chorus, voxel room fills with lights. End card.</t>
+    <t xml:space="preserve">0:00–0:03 “Based on a true story” over the voxel room in the dark (out on the beat). Then: Voxel diorama: 2020, a YouTube video on an old monitor shows a speedrunner in a cowboy hat (voxel, no face). The viewer makes a Twitch account that night and starts streaming retro games. CRT look: Ninja Gaiden-style pixel action, counter at 4 viewers. LED dot-matrix alert: RAID. It is the same speedrunner. The chat floods (kinetic type), stained-glass burst on the chorus, voxel room fills with lights. End card + credit: Story shared by a streamer on Reddit.</t>
   </si>
   <si>
     <t xml:space="preserve">chiptune pop-punk, triumphant and fast, 8-bit synth leads with live drums and driving bass, bright clear vocal, punchy modern production, 140 BPM</t>
   </si>
   <si>
-    <t xml:space="preserve">[Intro: 8-bit lead]
+    <t xml:space="preserve">[Intro: 2 bars, instrumental, 8-bit lead]
 [Verse]
 Twenty-twenty, found a video
 Cowboy hat and a speedrun
@@ -937,6 +940,12 @@
   </si>
   <si>
     <t xml:space="preserve">(pick from the Story Fisher shortlist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opens with “Based on a true story” (1.5 bars, 2.5–3 s, over the first shot). Rest written after the story is chosen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: 2 bars, instrumental] …</t>
   </si>
   <si>
     <t xml:space="preserve">Written after the story is chosen</t>
@@ -2632,14 +2641,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEEEEEE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFD5F2DC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -2649,6 +2650,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8D3D3"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEEEEEE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2922,7 +2931,7 @@
     <tabColor rgb="FF1F2430"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -3212,6 +3221,11 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="16" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3255,115 +3269,115 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M5" s="17" t="s">
         <v>39</v>
@@ -3382,49 +3396,49 @@
       </c>
       <c r="R5" s="17"/>
       <c r="S5" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="T5" s="17"/>
       <c r="U5" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>40</v>
@@ -3443,49 +3457,49 @@
       </c>
       <c r="R6" s="18"/>
       <c r="S6" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="T6" s="18"/>
       <c r="U6" s="18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>38</v>
@@ -3504,16 +3518,16 @@
       </c>
       <c r="R7" s="18"/>
       <c r="S7" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="T7" s="18"/>
       <c r="U7" s="18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -3522,14 +3536,14 @@
       <c r="F8" s="18"/>
       <c r="G8" s="18"/>
       <c r="H8" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L8" s="18"/>
       <c r="M8" s="5" t="s">
@@ -3551,12 +3565,12 @@
       <c r="S8" s="5"/>
       <c r="T8" s="18"/>
       <c r="U8" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -3565,14 +3579,14 @@
       <c r="F9" s="18"/>
       <c r="G9" s="18"/>
       <c r="H9" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" s="18"/>
       <c r="M9" s="5" t="s">
@@ -3594,12 +3608,12 @@
       <c r="S9" s="5"/>
       <c r="T9" s="18"/>
       <c r="U9" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -3608,14 +3622,14 @@
       <c r="F10" s="18"/>
       <c r="G10" s="18"/>
       <c r="H10" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I10" s="18"/>
       <c r="J10" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L10" s="18"/>
       <c r="M10" s="5" t="s">
@@ -3637,12 +3651,12 @@
       <c r="S10" s="5"/>
       <c r="T10" s="18"/>
       <c r="U10" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -3651,14 +3665,14 @@
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L11" s="18"/>
       <c r="M11" s="5" t="s">
@@ -3680,12 +3694,12 @@
       <c r="S11" s="5"/>
       <c r="T11" s="18"/>
       <c r="U11" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -3694,14 +3708,14 @@
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" s="18"/>
       <c r="M12" s="5" t="s">
@@ -3723,12 +3737,12 @@
       <c r="S12" s="5"/>
       <c r="T12" s="18"/>
       <c r="U12" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -3737,14 +3751,14 @@
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
       <c r="H13" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I13" s="18"/>
       <c r="J13" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L13" s="18"/>
       <c r="M13" s="5" t="s">
@@ -3766,7 +3780,7 @@
       <c r="S13" s="5"/>
       <c r="T13" s="18"/>
       <c r="U13" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -3935,122 +3949,122 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K5" s="18"/>
       <c r="L5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>38</v>
@@ -4073,44 +4087,44 @@
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K6" s="18"/>
       <c r="L6" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>38</v>
@@ -4133,44 +4147,44 @@
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K7" s="18"/>
       <c r="L7" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>38</v>
@@ -4193,44 +4207,44 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>38</v>
@@ -4253,44 +4267,44 @@
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K9" s="18"/>
       <c r="L9" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>38</v>
@@ -4313,44 +4327,44 @@
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K10" s="18"/>
       <c r="L10" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>38</v>
@@ -4373,44 +4387,44 @@
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K11" s="18"/>
       <c r="L11" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>38</v>
@@ -4433,44 +4447,44 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K12" s="18"/>
       <c r="L12" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>38</v>
@@ -4493,44 +4507,44 @@
     </row>
     <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K13" s="18"/>
       <c r="L13" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>38</v>
@@ -4553,44 +4567,44 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K14" s="18"/>
       <c r="L14" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O14" s="5" t="s">
         <v>38</v>
@@ -4613,44 +4627,44 @@
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K15" s="18"/>
       <c r="L15" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>38</v>
@@ -4673,44 +4687,44 @@
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K16" s="18"/>
       <c r="L16" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>38</v>
@@ -4733,44 +4747,44 @@
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K17" s="18"/>
       <c r="L17" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>38</v>
@@ -4793,44 +4807,44 @@
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O18" s="5" t="s">
         <v>38</v>
@@ -4853,44 +4867,44 @@
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>38</v>
@@ -4913,44 +4927,44 @@
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K20" s="18"/>
       <c r="L20" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O20" s="5" t="s">
         <v>38</v>
@@ -5132,82 +5146,82 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>38</v>
@@ -5227,30 +5241,30 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>38</v>
@@ -5270,41 +5284,41 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5312,22 +5326,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>38</v>
@@ -5339,22 +5353,22 @@
         <v>2</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>38</v>
@@ -5366,22 +5380,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>38</v>
@@ -5393,22 +5407,22 @@
         <v>4</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>38</v>
@@ -5420,22 +5434,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>38</v>
@@ -5625,877 +5639,901 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="337.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>120</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>140</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="I7" s="5"/>
+        <v>281</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="J7" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K7" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>288</v>
-      </c>
       <c r="C8" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="I8" s="5"/>
+        <v>281</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="J8" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K8" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>288</v>
-      </c>
       <c r="C9" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="I9" s="5"/>
+        <v>281</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="J9" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K9" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>288</v>
-      </c>
       <c r="C10" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="I10" s="5"/>
+        <v>281</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="J10" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K10" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>288</v>
-      </c>
       <c r="C11" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="I11" s="5"/>
+        <v>281</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="J11" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K11" s="18" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>288</v>
-      </c>
       <c r="C12" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="I12" s="5"/>
+        <v>281</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>291</v>
+      </c>
       <c r="J12" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K26" s="18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K27" s="18" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K28" s="18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>90</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K29" s="18" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>118</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -6559,58 +6597,58 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>38</v>
@@ -6618,24 +6656,24 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>368</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>365</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>38</v>
@@ -6646,16 +6684,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
@@ -6667,19 +6705,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>38</v>
@@ -6687,21 +6725,21 @@
       <c r="G8" s="18"/>
       <c r="H8" s="18"/>
       <c r="I8" s="18" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
@@ -6710,24 +6748,24 @@
       <c r="G9" s="18"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>38</v>
@@ -6735,24 +6773,24 @@
       <c r="G10" s="18"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>379</v>
-      </c>
       <c r="C11" s="5" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>38</v>
@@ -6760,24 +6798,24 @@
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>38</v>
@@ -6785,21 +6823,21 @@
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
@@ -6808,21 +6846,21 @@
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
@@ -6831,21 +6869,21 @@
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5" t="s">
@@ -6854,21 +6892,21 @@
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
@@ -6877,21 +6915,21 @@
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>399</v>
-      </c>
       <c r="C17" s="5" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
@@ -6900,24 +6938,24 @@
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>38</v>
@@ -6925,24 +6963,24 @@
       <c r="G18" s="18"/>
       <c r="H18" s="18"/>
       <c r="I18" s="18" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>38</v>
@@ -6950,24 +6988,24 @@
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>38</v>
@@ -6978,19 +7016,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>39</v>
@@ -6998,24 +7036,24 @@
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>38</v>
@@ -7023,24 +7061,24 @@
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>421</v>
-      </c>
       <c r="E23" s="5" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>38</v>
@@ -7048,24 +7086,24 @@
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>38</v>
@@ -7073,21 +7111,21 @@
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5" t="s">
@@ -7096,7 +7134,7 @@
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -7158,98 +7196,98 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>446</v>
-      </c>
       <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>38</v>
@@ -7258,19 +7296,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>38</v>
@@ -7279,19 +7317,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>38</v>
@@ -7300,19 +7338,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>38</v>
@@ -7321,42 +7359,42 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>467</v>
-      </c>
       <c r="F11" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>38</v>
@@ -7365,19 +7403,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>38</v>
@@ -7386,19 +7424,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>38</v>
@@ -7407,19 +7445,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>480</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>38</v>
@@ -7428,19 +7466,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>38</v>
@@ -7449,19 +7487,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>38</v>
@@ -7470,65 +7508,65 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>38</v>
@@ -7537,42 +7575,42 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>38</v>
@@ -7581,19 +7619,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>508</v>
-      </c>
       <c r="E23" s="5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>38</v>
@@ -7602,19 +7640,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>38</v>
@@ -7623,19 +7661,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>38</v>
@@ -7644,19 +7682,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>38</v>
@@ -7665,48 +7703,48 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>522</v>
-      </c>
       <c r="C28" s="5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -7781,32 +7819,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7814,19 +7852,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7834,19 +7872,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7854,19 +7892,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7874,19 +7912,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7894,19 +7932,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>556</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7914,19 +7952,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7934,19 +7972,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7954,19 +7992,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>569</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7974,19 +8012,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7994,29 +8032,29 @@
         <v>10</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>0.065</v>
@@ -8024,7 +8062,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B18" s="21" t="n">
         <v>0.013</v>
@@ -8032,7 +8070,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B19" s="21" t="n">
         <v>0.0033</v>
@@ -8040,55 +8078,55 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D24" s="22" t="n">
         <v>1</v>
@@ -8113,18 +8151,18 @@
         <v>0.0297</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D25" s="22" t="n">
         <v>7</v>
@@ -8149,18 +8187,18 @@
         <v>0.08085</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D26" s="22" t="n">
         <v>1</v>
@@ -8185,18 +8223,18 @@
         <v>0.0297</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D27" s="22" t="n">
         <v>7</v>
@@ -8221,18 +8259,18 @@
         <v>0.08085</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D28" s="22" t="n">
         <v>1</v>
@@ -8257,18 +8295,18 @@
         <v>0.0264</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D29" s="22" t="n">
         <v>7</v>
@@ -8293,18 +8331,18 @@
         <v>0.08085</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D30" s="22" t="n">
         <v>1</v>
@@ -8329,18 +8367,18 @@
         <v>0.0396</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D31" s="22" t="n">
         <v>1</v>
@@ -8365,12 +8403,12 @@
         <v>0.0231</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="24" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B32" s="24"/>
       <c r="C32" s="24"/>
@@ -8399,7 +8437,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="16" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -319,7 +319,7 @@
     <t xml:space="preserve">https://www.reddit.com/r/Twitch/comments/1pujw7y/</t>
   </si>
   <si>
-    <t xml:space="preserve">A desk-bound game streamer streams IRL at Christmas, peaks at 3 viewers; one viewer watches the train ride until the signal drops, then says it was amazing.</t>
+    <t xml:space="preserve">Christmas IRL tour, 3 viewers at peak; one viewer, who had never been on a train, watches the city turn to farmland until the signal drops and calls it an amazing stream.</t>
   </si>
   <si>
     <t xml:space="preserve">8, 15</t>
@@ -334,7 +334,7 @@
     <t xml:space="preserve">52 s</t>
   </si>
   <si>
-    <t xml:space="preserve">Anonymised retelling; ask the author before publishing</t>
+    <t xml:space="preserve">Anonymised retelling; permission DM drafted (in the script)</t>
   </si>
   <si>
     <t xml:space="preserve">Script: docs/scripts/ST-01_train-ride.md</t>
@@ -874,7 +874,7 @@
     <t xml:space="preserve">MV</t>
   </si>
   <si>
-    <t xml:space="preserve">0:00–0:03 “Based on a true story” over a slow push into the pixel city (out on the beat). Then: Pixel city at Christmas: a streamer who usually plays games at a desk steps outside, phone up, LIVE. Viewer counter climbs 1, 2, 3. On the evening train, rain streaks the window and the city slides past (hero shot). The signal bars fall, the picture freezes: signal lost. Black. The chat appears big, typed word by word: 'that was amazing. thank you'. Front-page halftone burst: 3 VIEWERS. ENOUGH. Back on the platform the streamer stops and reads it. The city turns warm; a small spark appears next to the message (companion cameo). End card + credit: Story shared by a streamer on Reddit.</t>
+    <t xml:space="preserve">0:00–0:03 “Based on a true story” over a slow push into the pixel city at dusk (out on the beat). A desk-bound game streamer takes the stream on a Christmas tour of their city: market lights, a castle, a lit carousel. Viewer counter climbs to 3. At the station they are about to end the stream; chat: 'wait, I've never been on a train'. Hero shot: through the window the city falls away into open farmland, fast. The signal bars drop, freeze, black. The chat fills the frame: 'thanks for being so chill. amazing stream'. Halftone burst: 3 VIEWERS. ENOUGH. Pull back over the fields and the globe to one lit window on the other side of the world; a small spark by the message (companion cameo). End card + credit: Story shared by a streamer on Reddit.</t>
   </si>
   <si>
     <t xml:space="preserve">warm lo-fi indie pop, gentle and hopeful, glockenspiel and felt piano, soft synth pads, brushed train-rhythm percussion, soft clear vocal up front, intimate dry production, 120 BPM</t>
@@ -885,27 +885,27 @@
   <si>
     <t xml:space="preserve">[Intro: 2 bars, instrumental, glockenspiel, train rhythm]
 [Verse: soft vocal]
-Took the stream outside on Christmas night
-Phone in my cold hand, city lights
+Took the stream out for Christmas in town
+Market lights, a castle, a carousel
 Three people watching, that's my crowd
 Talking to the street out loud
-Evening train, the windows run
-Rain on the glass, still on, still on
+Train to catch, I'll say goodbye
+"Wait, I've never been on a train"
 [Pre-Chorus: almost spoken]
-Signal fading
+Keep it on till the signal goes
 [Break]
 [Chorus: warm, fuller]
-You stayed till the signal died
-Said it was amazing, on a train at night
-Three is not nothing, three is enough
-Somebody was there, that's what it was
+You watched the city turn to fields
+Your first train, it moved so fast
+Said it was amazing, said thank you
+From the other side of the world
 [Outro: soft]
 That's why I do this
 That's why I do this
 [End]</t>
   </si>
   <si>
-    <t xml:space="preserve">Facts from the post only. Script: docs/scripts/ST-01_train-ride.md</t>
+    <t xml:space="preserve">APPROVED. v0.4: every line checked against the full post. Script: docs/scripts/ST-01_train-ride.md</t>
   </si>
   <si>
     <t xml:space="preserve">The raid from the hero</t>
@@ -2583,7 +2583,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDCEBFF"/>
+          <fgColor rgb="FFD5F2DC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2591,7 +2591,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFE7B3"/>
+          <fgColor rgb="FFDCEBFF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2641,7 +2641,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD5F2DC"/>
+          <fgColor rgb="FFF8D3D3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -2649,7 +2649,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF8D3D3"/>
+          <fgColor rgb="FFFFE7B3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="F6" s="5" t="n">
         <f aca="false">COUNTIF('1 Streamer Stories'!M6:M13,"Approved")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="5" t="n">
         <f aca="false">COUNTIF('1 Streamer Stories'!N6:N13,"Approved")</f>
@@ -3441,7 +3441,7 @@
         <v>99</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>38</v>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -874,7 +874,7 @@
     <t xml:space="preserve">MV</t>
   </si>
   <si>
-    <t xml:space="preserve">0:00–0:03 “Based on a true story” over a slow push into the pixel city at dusk (out on the beat). A desk-bound game streamer takes the stream on a Christmas tour of their city: market lights, a castle, a lit carousel. Viewer counter climbs to 3. At the station they are about to end the stream; chat: 'wait, I've never been on a train'. Hero shot: through the window the city falls away into open farmland, fast. The signal bars drop, freeze, black. The chat fills the frame: 'thanks for being so chill. amazing stream'. Halftone burst: 3 VIEWERS. ENOUGH. Pull back over the fields and the globe to one lit window on the other side of the world; a small spark by the message (companion cameo). End card + credit: Story shared by a streamer on Reddit.</t>
+    <t xml:space="preserve">0:00–0:03 “Based on a true story” over a slow push into the pixel city at dusk (out on the beat). A desk-bound game streamer takes the stream on a Christmas tour of their city: market lights, a castle, a lit carousel. Viewer counter climbs to 3. At the station they are about to end the stream; chat: 'wait, I've never been on a train'. Hero shot: through the window the city falls away into open farmland, fast. The signal bars drop, freeze, black. The chat fills the frame: 'thanks for being so chill. amazing stream'. Halftone burst: 3 VIEWERS. ENOUGH. Pull back over the fields and the globe to one lit window on the other side of the world; a small spark by the message (companion cameo). Line: They kept streaming IRL. End card + credit: Story shared by a streamer on Reddit.</t>
   </si>
   <si>
     <t xml:space="preserve">warm lo-fi indie pop, gentle and hopeful, glockenspiel and felt piano, soft synth pads, brushed train-rhythm percussion, soft clear vocal up front, intimate dry production, 120 BPM</t>
@@ -900,18 +900,19 @@
 Said it was amazing, said thank you
 From the other side of the world
 [Outro: soft]
-That's why I do this
-That's why I do this
+Like showing a visitor my town
+I saw it like a tourist too
+That's why it's worth it
 [End]</t>
   </si>
   <si>
-    <t xml:space="preserve">APPROVED. v0.4: every line checked against the full post. Script: docs/scripts/ST-01_train-ride.md</t>
+    <t xml:space="preserve">APPROVED. v0.5 (full picture: comments + later posts checked). v0.4: every line checked against the full post. Script: docs/scripts/ST-01_train-ride.md</t>
   </si>
   <si>
     <t xml:space="preserve">The raid from the hero</t>
   </si>
   <si>
-    <t xml:space="preserve">0:00–0:03 “Based on a true story” over the voxel room in the dark (out on the beat). Then: Voxel diorama: 2020, a YouTube video on an old monitor shows a speedrunner in a cowboy hat (voxel, no face). The viewer makes a Twitch account that night and starts streaming retro games. CRT look: Ninja Gaiden-style pixel action, counter at 4 viewers. LED dot-matrix alert: RAID. It is the same speedrunner. The chat floods (kinetic type), stained-glass burst on the chorus, voxel room fills with lights. End card + credit: Story shared by a streamer on Reddit.</t>
+    <t xml:space="preserve">0:00–0:03 “Based on a true story” over the voxel room in the dark (out on the beat). Then: Voxel diorama: 2020, a YouTube video on an old monitor shows a speedrunner in a cowboy hat (voxel, no face). The viewer makes a Twitch account that night and starts streaming retro games. CRT look: Ninja Gaiden-style pixel action, chasing a personal best, counter at 4 viewers. LED dot-matrix alert: RAID · 450. It is the same speedrunner. The chat floods (kinetic type), stained-glass burst on the chorus, voxel room fills with lights. End card + credit: Story shared by a streamer on Reddit.</t>
   </si>
   <si>
     <t xml:space="preserve">chiptune pop-punk, triumphant and fast, 8-bit synth leads with live drums and driving bass, bright clear vocal, punchy modern production, 140 BPM</t>
@@ -924,19 +925,19 @@
 Made an account that very night
 Started streaming the old games
 [Pre-Chorus: building]
-Four people watching, Ninja Gaiden on
+Four people watching, chasing my best
 [Break]
 [Chorus: full band, shout-along]
 Then the raid came in, it was him
+Four hundred fifty people in
 The one who started all of this
-Look who's in my chat tonight
 Look who's watching now
 [Outro]
 Look who's watching now
 [End]</t>
   </si>
   <si>
-    <t xml:space="preserve">Facts from the post (Story Fisher, quality 9). Never name the speedrunner. Check the full post before scripting.</t>
+    <t xml:space="preserve">Full picture checked (75 comments): arc complete, no follow-ups; raid was 450 viewers while chasing a PB with 4. Never name the speedrunner. Not yet approved.</t>
   </si>
   <si>
     <t xml:space="preserve">(pick from the Story Fisher shortlist)</t>
@@ -5682,7 +5683,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="337.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="351" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>91</v>
       </c>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -877,13 +877,13 @@
     <t xml:space="preserve">0:00–0:03 “Based on a true story” over a slow push into the pixel city at dusk (out on the beat). A desk-bound game streamer takes the stream on a Christmas tour of their city: market lights, a castle, a lit carousel. Viewer counter climbs to 3. At the station they are about to end the stream; chat: 'wait, I've never been on a train'. Hero shot: through the window the city falls away into open farmland, fast. The signal bars drop, freeze, black. The chat fills the frame: 'thanks for being so chill. amazing stream'. Halftone burst: 3 VIEWERS. ENOUGH. Pull back over the fields and the globe to one lit window on the other side of the world; a small spark by the message (companion cameo). Line: They kept streaming IRL. End card + credit: Story shared by a streamer on Reddit.</t>
   </si>
   <si>
-    <t xml:space="preserve">warm lo-fi indie pop, gentle and hopeful, glockenspiel and felt piano, soft synth pads, brushed train-rhythm percussion, soft clear vocal up front, intimate dry production, 120 BPM</t>
+    <t xml:space="preserve">catchy upbeat indie pop, warm and hopeful, glockenspiel hook from the first second, train-rhythm drums with handclaps, bright felt piano, clear warm vocal up front, singalong chorus, crisp modern production, 120 BPM</t>
   </si>
   <si>
     <t xml:space="preserve">heavy reverb, autotune, rap verses, spoken word intro, long instrumental intro</t>
   </si>
   <si>
-    <t xml:space="preserve">[Intro: 2 bars, instrumental, glockenspiel, train rhythm]
+    <t xml:space="preserve">[Intro: 2 bars, glockenspiel hook, train-rhythm drums]
 [Verse: soft vocal]
 Took the stream out for Christmas in town
 Market lights, a castle, a carousel
@@ -891,22 +891,23 @@
 Talking to the street out loud
 Train to catch, I'll say goodbye
 "Wait, I've never been on a train"
-[Pre-Chorus: almost spoken]
-Keep it on till the signal goes
+[Pre-Chorus: rising]
+"Can you keep it on?"
 [Break]
-[Chorus: warm, fuller]
+[Chorus: catchy singalong, full drums, glockenspiel hook]
+Keep it on, keep it on, till the signal's gone
 You watched the city turn to fields
 Your first train, it moved so fast
-Said it was amazing, said thank you
-From the other side of the world
-[Outro: soft]
+Keep it on, keep it on, till the signal's gone
+Said it was amazing, from the other side of the world
+[Outro: soft, glockenspiel hook returns]
 Like showing a visitor my town
 I saw it like a tourist too
 That's why it's worth it
 [End]</t>
   </si>
   <si>
-    <t xml:space="preserve">APPROVED. v0.5 (full picture: comments + later posts checked). v0.4: every line checked against the full post. Script: docs/scripts/ST-01_train-ride.md</t>
+    <t xml:space="preserve">APPROVED. v0.6 catchier (hook from second 0, repeated chorus line from the story). v0.5 (full picture: comments + later posts checked). v0.4: every line checked against the full post. Script: docs/scripts/ST-01_train-ride.md</t>
   </si>
   <si>
     <t xml:space="preserve">The raid from the hero</t>
@@ -5683,7 +5684,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="351" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="363.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>91</v>
       </c>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="619">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -328,16 +328,16 @@
     <t xml:space="preserve">Pixel art → Neon line · Halftone</t>
   </si>
   <si>
-    <t xml:space="preserve">Warm lo-fi indie pop, 120 BPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52 s</t>
+    <t xml:space="preserve">Catchy upbeat indie pop, 123 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈61 s (58.3 s song + end card)</t>
   </si>
   <si>
     <t xml:space="preserve">Anonymised retelling; permission DM drafted (in the script)</t>
   </si>
   <si>
-    <t xml:space="preserve">Script: docs/scripts/ST-01_train-ride.md</t>
+    <t xml:space="preserve">Script: docs/scripts/ST-01_train-ride.md · 2026-10-04: song approved (master song_with_intro.wav); script v0.7 retimed. Next: style frames.</t>
   </si>
   <si>
     <t xml:space="preserve">ST-02</t>
@@ -872,6 +872,9 @@
   </si>
   <si>
     <t xml:space="preserve">MV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3 s song (≈61 s film)</t>
   </si>
   <si>
     <t xml:space="preserve">0:00–0:03 “Based on a true story” over a slow push into the pixel city at dusk (out on the beat). A desk-bound game streamer takes the stream on a Christmas tour of their city: market lights, a castle, a lit carousel. Viewer counter climbs to 3. At the station they are about to end the stream; chat: 'wait, I've never been on a train'. Hero shot: through the window the city falls away into open farmland, fast. The signal bars drop, freeze, black. The chat fills the frame: 'thanks for being so chill. amazing stream'. Halftone burst: 3 VIEWERS. ENOUGH. Pull back over the fields and the globe to one lit window on the other side of the world; a small spark by the message (companion cameo). Line: They kept streaming IRL. End card + credit: Story shared by a streamer on Reddit.</t>
@@ -907,7 +910,7 @@
 [End]</t>
   </si>
   <si>
-    <t xml:space="preserve">APPROVED. v0.6 catchier (hook from second 0, repeated chorus line from the story). v0.5 (full picture: comments + later posts checked). v0.4: every line checked against the full post. Script: docs/scripts/ST-01_train-ride.md</t>
+    <t xml:space="preserve">Song approved 2026-10-04: Suno take + 2-bar intro spliced from its own hook; lines 9–10 sung slightly differently, subtitles show the written lyric. APPROVED. v0.6 catchier (hook from second 0, repeated chorus line from the story). v0.5 (full picture: comments + later posts checked). v0.4: every line checked against the full post. Script: docs/scripts/ST-01_train-ride.md</t>
   </si>
   <si>
     <t xml:space="preserve">The raid from the hero</t>
@@ -2062,25 +2065,7 @@
     <t xml:space="preserve">S++</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2430"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">《光先到》 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2430"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ pdoom 4K</t>
-    </r>
+    <t xml:space="preserve">《光先到》 / pdoom 4K</t>
   </si>
   <si>
     <t xml:space="preserve">Every shot a hero shot, 4K60 path-traced look</t>
@@ -2294,6 +2279,7 @@
       <color rgb="FF1F2430"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -2428,20 +2414,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2453,47 +2443,47 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2509,11 +2499,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2525,11 +2515,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2936,297 +2926,297 @@
   <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <f aca="false">COUNTA('1 Streamer Stories'!A6:A13)</f>
         <v>8</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <f aca="false">COUNTIF('1 Streamer Stories'!M6:M13,"Approved")</f>
         <v>1</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <f aca="false">COUNTIF('1 Streamer Stories'!N6:N13,"Approved")</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <f aca="false">COUNTIF('1 Streamer Stories'!Q6:Q13,"Approved")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <f aca="false">COUNTA('2 Brand · Generic'!A5:A20)</f>
         <v>16</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <f aca="false">COUNTIF('2 Brand · Generic'!O5:O20,"Approved")</f>
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <f aca="false">COUNTIF('2 Brand · Generic'!P5:P20,"Approved")</f>
         <v>0</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <f aca="false">COUNTIF('2 Brand · Generic'!S5:S20,"Approved")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <f aca="false">COUNTA('3 Brand · Master'!A5:A6)</f>
         <v>2</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <f aca="false">COUNTIF('3 Brand · Master'!H5:H6,"Approved")</f>
         <v>0</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <f aca="false">COUNTIF('3 Brand · Master'!I5:I6,"Approved")</f>
         <v>0</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="6" t="n">
         <f aca="false">COUNTIF('3 Brand · Master'!L5:L6,"Approved")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3250,538 +3240,538 @@
   <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="13" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="13" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="U4" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="17" t="s">
+      <c r="L5" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="P5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17" t="s">
+      <c r="N5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q5" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17" t="s">
+      <c r="T5" s="18"/>
+      <c r="U5" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R6" s="18"/>
-      <c r="S6" s="5" t="s">
+      <c r="N6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R6" s="19"/>
+      <c r="S6" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18" t="s">
+      <c r="T6" s="19"/>
+      <c r="U6" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R7" s="18"/>
-      <c r="S7" s="5" t="s">
+      <c r="M7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" s="19"/>
+      <c r="S7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18" t="s">
+      <c r="T7" s="19"/>
+      <c r="U7" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="5" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="5" t="s">
+      <c r="I8" s="19"/>
+      <c r="J8" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="L8" s="18"/>
-      <c r="M8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R8" s="18"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18" t="s">
+      <c r="L8" s="19"/>
+      <c r="M8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R8" s="19"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="5" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="I9" s="18"/>
-      <c r="J9" s="5" t="s">
+      <c r="I9" s="19"/>
+      <c r="J9" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="L9" s="18"/>
-      <c r="M9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R9" s="18"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18" t="s">
+      <c r="L9" s="19"/>
+      <c r="M9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R9" s="19"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="5" t="s">
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="I10" s="18"/>
-      <c r="J10" s="5" t="s">
+      <c r="I10" s="19"/>
+      <c r="J10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R10" s="18"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18" t="s">
+      <c r="L10" s="19"/>
+      <c r="M10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R10" s="19"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="5" t="s">
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="I11" s="18"/>
-      <c r="J11" s="5" t="s">
+      <c r="I11" s="19"/>
+      <c r="J11" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="L11" s="18"/>
-      <c r="M11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R11" s="18"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18" t="s">
+      <c r="L11" s="19"/>
+      <c r="M11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R11" s="19"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="5" t="s">
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="I12" s="18"/>
-      <c r="J12" s="5" t="s">
+      <c r="I12" s="19"/>
+      <c r="J12" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R12" s="18"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18" t="s">
+      <c r="L12" s="19"/>
+      <c r="M12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R12" s="19"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="5" t="s">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="5" t="s">
+      <c r="I13" s="19"/>
+      <c r="J13" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R13" s="18"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18" t="s">
+      <c r="L13" s="19"/>
+      <c r="M13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R13" s="19"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19" t="s">
         <v>115</v>
       </c>
     </row>
@@ -3929,1063 +3919,1063 @@
   <dimension ref="A1:V20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="15" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="15" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="U4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="V4" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K5" s="18"/>
-      <c r="L5" s="5" t="s">
+      <c r="K5" s="19"/>
+      <c r="L5" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T5" s="18"/>
-      <c r="U5" s="18"/>
-      <c r="V5" s="18"/>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="O5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T5" s="19"/>
+      <c r="U5" s="19"/>
+      <c r="V5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K6" s="18"/>
-      <c r="L6" s="5" t="s">
+      <c r="K6" s="19"/>
+      <c r="L6" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="N6" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="18"/>
-    </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="O6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K7" s="18"/>
-      <c r="L7" s="5" t="s">
+      <c r="K7" s="19"/>
+      <c r="L7" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="N7" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T7" s="18"/>
-      <c r="U7" s="18"/>
-      <c r="V7" s="18"/>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="O7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K8" s="18"/>
-      <c r="L8" s="5" t="s">
+      <c r="K8" s="19"/>
+      <c r="L8" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N8" s="5" t="s">
+      <c r="N8" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
-      <c r="V8" s="18"/>
-    </row>
-    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="O8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
+    </row>
+    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="5" t="s">
+      <c r="K9" s="19"/>
+      <c r="L9" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N9" s="5" t="s">
+      <c r="N9" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
-      <c r="V9" s="18"/>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="O9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K10" s="18"/>
-      <c r="L10" s="5" t="s">
+      <c r="K10" s="19"/>
+      <c r="L10" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="N10" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="18"/>
-    </row>
-    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="O10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="5" t="s">
+      <c r="K11" s="19"/>
+      <c r="L11" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="N11" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="18"/>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="O11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+    </row>
+    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K12" s="18"/>
-      <c r="L12" s="5" t="s">
+      <c r="K12" s="19"/>
+      <c r="L12" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N12" s="5" t="s">
+      <c r="N12" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="18"/>
-    </row>
-    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="O12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K13" s="18"/>
-      <c r="L13" s="5" t="s">
+      <c r="K13" s="19"/>
+      <c r="L13" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N13" s="5" t="s">
+      <c r="N13" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="18"/>
-    </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="O13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K14" s="18"/>
-      <c r="L14" s="5" t="s">
+      <c r="K14" s="19"/>
+      <c r="L14" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N14" s="5" t="s">
+      <c r="N14" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-      <c r="V14" s="18"/>
-    </row>
-    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="O14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K15" s="18"/>
-      <c r="L15" s="5" t="s">
+      <c r="K15" s="19"/>
+      <c r="L15" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="M15" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N15" s="5" t="s">
+      <c r="N15" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="18"/>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="O15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K16" s="18"/>
-      <c r="L16" s="5" t="s">
+      <c r="K16" s="19"/>
+      <c r="L16" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N16" s="5" t="s">
+      <c r="N16" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T16" s="18"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="18"/>
-    </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="O16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K17" s="18"/>
-      <c r="L17" s="5" t="s">
+      <c r="K17" s="19"/>
+      <c r="L17" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="M17" s="5" t="s">
+      <c r="M17" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N17" s="5" t="s">
+      <c r="N17" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
-      <c r="V17" s="18"/>
-    </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="O17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K18" s="18"/>
-      <c r="L18" s="5" t="s">
+      <c r="K18" s="19"/>
+      <c r="L18" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="M18" s="5" t="s">
+      <c r="M18" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N18" s="5" t="s">
+      <c r="N18" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="18"/>
-    </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="O18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K19" s="18"/>
-      <c r="L19" s="5" t="s">
+      <c r="K19" s="19"/>
+      <c r="L19" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="M19" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N19" s="5" t="s">
+      <c r="N19" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="18"/>
-    </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="O19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="K20" s="18"/>
-      <c r="L20" s="5" t="s">
+      <c r="K20" s="19"/>
+      <c r="L20" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="M20" s="5" t="s">
+      <c r="M20" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N20" s="5" t="s">
+      <c r="N20" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="O20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
+      <c r="O20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:V20"/>
@@ -5131,332 +5121,332 @@
   <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18" t="s">
+      <c r="H5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18" t="s">
+      <c r="H6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" s="18"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+      <c r="H10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="18"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+      <c r="H11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="19"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="18"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+      <c r="H12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I13" s="18"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+      <c r="H13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" s="18"/>
+      <c r="H14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A9:I14"/>
@@ -5626,916 +5616,916 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="363.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="5" t="n">
+      <c r="D5" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="B10" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="18" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="I10" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="D11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="18" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C13" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="18" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="18" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E30" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="18" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="18" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" s="18" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K13" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K21" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K23" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K24" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K25" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K27" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K28" s="18" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K29" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="G30" s="5" t="s">
+      <c r="F30" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="H30" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I30" s="5" t="s">
+      <c r="G30" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="J30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K30" s="18" t="s">
+      <c r="H30" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="I30" s="6" t="s">
         <v>356</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -6586,557 +6576,557 @@
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="36"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A1" s="2" t="s">
         <v>358</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="H4" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18" t="s">
+      <c r="C6" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="F6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="E10" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18" t="s">
+      <c r="C22" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="D23" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18" t="s">
+      <c r="C24" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+      <c r="F24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19" t="s">
         <v>432</v>
       </c>
-      <c r="B25" s="5" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18" t="s">
+      <c r="D25" s="6" t="s">
         <v>436</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -7187,566 +7177,566 @@
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A1" s="2" t="s">
         <v>438</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="18" t="s">
+      <c r="E5" s="6" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="F5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="19" t="s">
         <v>451</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C6" s="5" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="B6" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="18" t="s">
+      <c r="D6" s="6" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="E6" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="19" t="s">
         <v>455</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C7" s="5" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="B7" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="F7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="B8" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="F8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="19"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="B9" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="F9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="B10" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="F10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="B11" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="18" t="s">
+      <c r="E16" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="F17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="B18" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="18" t="s">
+      <c r="D18" s="6" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="E18" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="19" t="s">
         <v>496</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C19" s="5" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="B19" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="18" t="s">
+      <c r="D19" s="6" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="E19" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C20" s="5" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="B20" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="18"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="D20" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="E20" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="B21" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="F21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="18" t="s">
+      <c r="E21" s="6" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="F21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="19" t="s">
         <v>508</v>
       </c>
-      <c r="B22" s="5" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
         <v>509</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="D22" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="18"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="F22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="B23" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="E23" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="B24" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+      <c r="D24" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="F24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="18"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="D25" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="E25" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="B26" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G26" s="18"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="D26" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="E26" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="C27" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="F27" s="5" t="s">
+      <c r="C28" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G27" s="18" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>529</v>
+      <c r="G28" s="19" t="s">
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -7808,638 +7798,638 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A1" s="2" t="s">
         <v>531</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="F4" s="5" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="F5" s="6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="F6" s="6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="F7" s="6" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="F8" s="6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+    </row>
+    <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>562</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+      <c r="F10" s="6" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>567</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>568</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+      <c r="F11" s="6" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+    </row>
+    <row r="13" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+      <c r="F13" s="6" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="B14" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="20" t="s">
         <v>581</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>583</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+      <c r="F14" s="6" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
         <v>585</v>
       </c>
-      <c r="B17" s="21" t="n">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="B17" s="22" t="n">
         <v>0.065</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="B18" s="21" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="B18" s="22" t="n">
         <v>0.013</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="B19" s="21" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="B19" s="22" t="n">
         <v>0.0033</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
         <v>589</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>590</v>
+      </c>
+    </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="C23" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="G23" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="I23" s="5" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="B24" s="5" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="D24" s="22" t="n">
+      <c r="C24" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="D24" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="22" t="n">
+      <c r="E24" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="6" t="n">
         <f aca="false">D24*E24</f>
         <v>9</v>
       </c>
-      <c r="G24" s="23" t="n">
+      <c r="G24" s="24" t="n">
         <f aca="false">F24*$B$17</f>
         <v>0.585</v>
       </c>
-      <c r="H24" s="23" t="n">
+      <c r="H24" s="24" t="n">
         <f aca="false">F24*$B$18</f>
         <v>0.117</v>
       </c>
-      <c r="I24" s="23" t="n">
+      <c r="I24" s="24" t="n">
         <f aca="false">F24*$B$19</f>
         <v>0.0297</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="6" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="E25" s="22" t="n">
+      <c r="E25" s="23" t="n">
         <v>3.5</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="6" t="n">
         <f aca="false">D25*E25</f>
         <v>24.5</v>
       </c>
-      <c r="G25" s="23" t="n">
+      <c r="G25" s="24" t="n">
         <f aca="false">F25*$B$17</f>
         <v>1.5925</v>
       </c>
-      <c r="H25" s="23" t="n">
+      <c r="H25" s="24" t="n">
         <f aca="false">F25*$B$18</f>
         <v>0.3185</v>
       </c>
-      <c r="I25" s="23" t="n">
+      <c r="I25" s="24" t="n">
         <f aca="false">F25*$B$19</f>
         <v>0.08085</v>
       </c>
-      <c r="J25" s="5" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="J25" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="B26" s="5" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="D26" s="22" t="n">
+      <c r="C26" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="D26" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="22" t="n">
+      <c r="E26" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="6" t="n">
         <f aca="false">D26*E26</f>
         <v>9</v>
       </c>
-      <c r="G26" s="23" t="n">
+      <c r="G26" s="24" t="n">
         <f aca="false">F26*$B$17</f>
         <v>0.585</v>
       </c>
-      <c r="H26" s="23" t="n">
+      <c r="H26" s="24" t="n">
         <f aca="false">F26*$B$18</f>
         <v>0.117</v>
       </c>
-      <c r="I26" s="23" t="n">
+      <c r="I26" s="24" t="n">
         <f aca="false">F26*$B$19</f>
         <v>0.0297</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="6" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="22" t="n">
+      <c r="E27" s="23" t="n">
         <v>3.5</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="6" t="n">
         <f aca="false">D27*E27</f>
         <v>24.5</v>
       </c>
-      <c r="G27" s="23" t="n">
+      <c r="G27" s="24" t="n">
         <f aca="false">F27*$B$17</f>
         <v>1.5925</v>
       </c>
-      <c r="H27" s="23" t="n">
+      <c r="H27" s="24" t="n">
         <f aca="false">F27*$B$18</f>
         <v>0.3185</v>
       </c>
-      <c r="I27" s="23" t="n">
+      <c r="I27" s="24" t="n">
         <f aca="false">F27*$B$19</f>
         <v>0.08085</v>
       </c>
-      <c r="J27" s="5" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
+      <c r="J27" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="B28" s="5" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="D28" s="22" t="n">
+      <c r="C28" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="D28" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="22" t="n">
+      <c r="E28" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="6" t="n">
         <f aca="false">D28*E28</f>
         <v>8</v>
       </c>
-      <c r="G28" s="23" t="n">
+      <c r="G28" s="24" t="n">
         <f aca="false">F28*$B$17</f>
         <v>0.52</v>
       </c>
-      <c r="H28" s="23" t="n">
+      <c r="H28" s="24" t="n">
         <f aca="false">F28*$B$18</f>
         <v>0.104</v>
       </c>
-      <c r="I28" s="23" t="n">
+      <c r="I28" s="24" t="n">
         <f aca="false">F28*$B$19</f>
         <v>0.0264</v>
       </c>
-      <c r="J28" s="5" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+      <c r="J28" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="B29" s="5" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="D29" s="22" t="n">
+      <c r="C29" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="D29" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="E29" s="22" t="n">
+      <c r="E29" s="23" t="n">
         <v>3.5</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="6" t="n">
         <f aca="false">D29*E29</f>
         <v>24.5</v>
       </c>
-      <c r="G29" s="23" t="n">
+      <c r="G29" s="24" t="n">
         <f aca="false">F29*$B$17</f>
         <v>1.5925</v>
       </c>
-      <c r="H29" s="23" t="n">
+      <c r="H29" s="24" t="n">
         <f aca="false">F29*$B$18</f>
         <v>0.3185</v>
       </c>
-      <c r="I29" s="23" t="n">
+      <c r="I29" s="24" t="n">
         <f aca="false">F29*$B$19</f>
         <v>0.08085</v>
       </c>
-      <c r="J29" s="5" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+      <c r="J29" s="6" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="D30" s="22" t="n">
+      <c r="C30" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="D30" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="6" t="n">
         <f aca="false">D30*E30</f>
         <v>12</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G30" s="24" t="n">
         <f aca="false">F30*$B$17</f>
         <v>0.78</v>
       </c>
-      <c r="H30" s="23" t="n">
+      <c r="H30" s="24" t="n">
         <f aca="false">F30*$B$18</f>
         <v>0.156</v>
       </c>
-      <c r="I30" s="23" t="n">
+      <c r="I30" s="24" t="n">
         <f aca="false">F30*$B$19</f>
         <v>0.0396</v>
       </c>
-      <c r="J30" s="5" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
+      <c r="J30" s="6" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="D31" s="22" t="n">
+      <c r="C31" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="D31" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="22" t="n">
+      <c r="E31" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="6" t="n">
         <f aca="false">D31*E31</f>
         <v>7</v>
       </c>
-      <c r="G31" s="23" t="n">
+      <c r="G31" s="24" t="n">
         <f aca="false">F31*$B$17</f>
         <v>0.455</v>
       </c>
-      <c r="H31" s="23" t="n">
+      <c r="H31" s="24" t="n">
         <f aca="false">F31*$B$18</f>
         <v>0.091</v>
       </c>
-      <c r="I31" s="23" t="n">
+      <c r="I31" s="24" t="n">
         <f aca="false">F31*$B$19</f>
         <v>0.0231</v>
       </c>
-      <c r="J31" s="5" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24" t="s">
+      <c r="J31" s="6" t="s">
         <v>616</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24" t="n">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="25" t="s">
+        <v>617</v>
+      </c>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25" t="n">
         <f aca="false">SUM(D24:D31)</f>
         <v>26</v>
       </c>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24" t="n">
+      <c r="E32" s="25"/>
+      <c r="F32" s="25" t="n">
         <f aca="false">SUM(F24:F31)</f>
         <v>118.5</v>
       </c>
-      <c r="G32" s="25" t="n">
+      <c r="G32" s="26" t="n">
         <f aca="false">SUM(G24:G31)</f>
         <v>7.7025</v>
       </c>
-      <c r="H32" s="25" t="n">
+      <c r="H32" s="26" t="n">
         <f aca="false">SUM(H24:H31)</f>
         <v>1.5405</v>
       </c>
-      <c r="I32" s="25" t="n">
+      <c r="I32" s="26" t="n">
         <f aca="false">SUM(I24:I31)</f>
         <v>0.39105</v>
       </c>
-      <c r="J32" s="24"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="s">
-        <v>617</v>
+      <c r="J32" s="25"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -337,7 +337,7 @@
     <t xml:space="preserve">Anonymised retelling; permission DM drafted (in the script)</t>
   </si>
   <si>
-    <t xml:space="preserve">Script: docs/scripts/ST-01_train-ride.md · 2026-10-04: song approved (master song_with_intro.wav); script v0.7 retimed. Next: style frames.</t>
+    <t xml:space="preserve">Script: docs/scripts/ST-01_train-ride.md · 2026-10-04: song approved (master song_with_intro.wav); script v0.7 retimed. Next: style frames. · 2026-10-04: style frames approved (13 scenes, no on-screen people, the phone is the protagonist); quality band 6–10. Animatic rendering.</t>
   </si>
   <si>
     <t xml:space="preserve">ST-02</t>
@@ -3439,10 +3439,10 @@
         <v>41</v>
       </c>
       <c r="O6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="Q6" s="6" t="s">
         <v>38</v>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="621">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -268,6 +268,9 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
+    <t xml:space="preserve">Post description (short caption)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ST-EX</t>
   </si>
   <si>
@@ -338,6 +341,9 @@
   </si>
   <si>
     <t xml:space="preserve">Script: docs/scripts/ST-01_train-ride.md · 2026-10-04: song approved (master song_with_intro.wav); script v0.7 retimed. Next: style frames. · 2026-10-04: style frames approved (13 scenes, no on-screen people, the phone is the protagonist); quality band 6–10. Animatic rendering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A streamer's first real IRL. 3 viewers. One of them had never been on a train. Based on a true story.</t>
   </si>
   <si>
     <t xml:space="preserve">ST-02</t>
@@ -3237,7 +3243,7 @@
     <tabColor rgb="FF7A5AF8"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -3257,6 +3263,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3333,43 +3340,46 @@
       <c r="U4" s="5" t="s">
         <v>76</v>
       </c>
+      <c r="V4" s="5" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M5" s="18" t="s">
         <v>39</v>
@@ -3388,49 +3398,49 @@
       </c>
       <c r="R5" s="18"/>
       <c r="S5" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T5" s="18"/>
       <c r="U5" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>41</v>
@@ -3449,49 +3459,52 @@
       </c>
       <c r="R6" s="19"/>
       <c r="S6" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T6" s="19"/>
       <c r="U6" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L7" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>38</v>
@@ -3510,16 +3523,16 @@
       </c>
       <c r="R7" s="19"/>
       <c r="S7" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T7" s="19"/>
       <c r="U7" s="19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -3528,14 +3541,14 @@
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
       <c r="H8" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I8" s="19"/>
       <c r="J8" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L8" s="19"/>
       <c r="M8" s="6" t="s">
@@ -3557,12 +3570,12 @@
       <c r="S8" s="6"/>
       <c r="T8" s="19"/>
       <c r="U8" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -3571,14 +3584,14 @@
       <c r="F9" s="19"/>
       <c r="G9" s="19"/>
       <c r="H9" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L9" s="19"/>
       <c r="M9" s="6" t="s">
@@ -3600,12 +3613,12 @@
       <c r="S9" s="6"/>
       <c r="T9" s="19"/>
       <c r="U9" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3614,14 +3627,14 @@
       <c r="F10" s="19"/>
       <c r="G10" s="19"/>
       <c r="H10" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I10" s="19"/>
       <c r="J10" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L10" s="19"/>
       <c r="M10" s="6" t="s">
@@ -3643,12 +3656,12 @@
       <c r="S10" s="6"/>
       <c r="T10" s="19"/>
       <c r="U10" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -3657,14 +3670,14 @@
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
       <c r="H11" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L11" s="19"/>
       <c r="M11" s="6" t="s">
@@ -3686,12 +3699,12 @@
       <c r="S11" s="6"/>
       <c r="T11" s="19"/>
       <c r="U11" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -3700,14 +3713,14 @@
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
       <c r="H12" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I12" s="19"/>
       <c r="J12" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L12" s="19"/>
       <c r="M12" s="6" t="s">
@@ -3729,12 +3742,12 @@
       <c r="S12" s="6"/>
       <c r="T12" s="19"/>
       <c r="U12" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -3743,14 +3756,14 @@
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
       <c r="H13" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L13" s="19"/>
       <c r="M13" s="6" t="s">
@@ -3772,7 +3785,7 @@
       <c r="S13" s="6"/>
       <c r="T13" s="19"/>
       <c r="U13" s="19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3941,12 +3954,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3954,37 +3967,37 @@
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>62</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>65</v>
@@ -4019,44 +4032,44 @@
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K5" s="19"/>
       <c r="L5" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O5" s="6" t="s">
         <v>38</v>
@@ -4079,44 +4092,44 @@
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>38</v>
@@ -4139,44 +4152,44 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K7" s="19"/>
       <c r="L7" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>38</v>
@@ -4199,44 +4212,44 @@
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="I8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>38</v>
@@ -4259,44 +4272,44 @@
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>38</v>
@@ -4319,44 +4332,44 @@
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>167</v>
-      </c>
       <c r="I10" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>38</v>
@@ -4379,44 +4392,44 @@
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>38</v>
@@ -4439,44 +4452,44 @@
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>176</v>
-      </c>
       <c r="J12" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K12" s="19"/>
       <c r="L12" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>38</v>
@@ -4499,44 +4512,44 @@
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>38</v>
@@ -4559,44 +4572,44 @@
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>185</v>
-      </c>
       <c r="I14" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>38</v>
@@ -4619,44 +4632,44 @@
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>38</v>
@@ -4679,44 +4692,44 @@
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>194</v>
-      </c>
       <c r="I16" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>38</v>
@@ -4739,44 +4752,44 @@
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>38</v>
@@ -4799,44 +4812,44 @@
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>204</v>
-      </c>
       <c r="J18" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
@@ -4859,44 +4872,44 @@
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>38</v>
@@ -4919,44 +4932,44 @@
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>213</v>
-      </c>
       <c r="I20" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>38</v>
@@ -5138,12 +5151,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5151,13 +5164,13 @@
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>66</v>
@@ -5166,7 +5179,7 @@
         <v>65</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>68</v>
@@ -5195,25 +5208,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>38</v>
@@ -5233,30 +5246,30 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
       <c r="O5" s="19" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>38</v>
@@ -5276,38 +5289,38 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
       <c r="O6" s="19" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>76</v>
@@ -5318,22 +5331,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>38</v>
@@ -5345,22 +5358,22 @@
         <v>2</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>38</v>
@@ -5372,22 +5385,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>38</v>
@@ -5399,22 +5412,22 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>38</v>
@@ -5426,22 +5439,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>38</v>
@@ -5631,12 +5644,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5644,31 +5657,31 @@
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>76</v>
@@ -5676,856 +5689,856 @@
     </row>
     <row r="5" customFormat="false" ht="363.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>123</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>41</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>140</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>90</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -6589,38 +6602,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>76</v>
@@ -6628,19 +6641,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>38</v>
@@ -6648,24 +6661,24 @@
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>371</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>369</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>38</v>
@@ -6676,16 +6689,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
@@ -6697,19 +6710,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>38</v>
@@ -6717,21 +6730,21 @@
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
@@ -6740,24 +6753,24 @@
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="19" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>38</v>
@@ -6765,24 +6778,24 @@
       <c r="G10" s="19"/>
       <c r="H10" s="19"/>
       <c r="I10" s="19" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>38</v>
@@ -6790,24 +6803,24 @@
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>387</v>
-      </c>
       <c r="D12" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>38</v>
@@ -6815,21 +6828,21 @@
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
       <c r="I12" s="19" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
@@ -6838,21 +6851,21 @@
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
       <c r="I13" s="19" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
@@ -6861,21 +6874,21 @@
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
       <c r="I14" s="19" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
@@ -6884,21 +6897,21 @@
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
@@ -6907,21 +6920,21 @@
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
       <c r="I16" s="19" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
@@ -6930,24 +6943,24 @@
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
       <c r="I17" s="19" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>407</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>38</v>
@@ -6955,24 +6968,24 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>38</v>
@@ -6980,24 +6993,24 @@
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
       <c r="I19" s="19" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>413</v>
-      </c>
       <c r="C20" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>38</v>
@@ -7008,19 +7021,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>39</v>
@@ -7028,24 +7041,24 @@
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>38</v>
@@ -7053,24 +7066,24 @@
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>426</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>38</v>
@@ -7078,24 +7091,24 @@
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>38</v>
@@ -7103,21 +7116,21 @@
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6" t="s">
@@ -7126,7 +7139,7 @@
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -7188,32 +7201,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>76</v>
@@ -7221,65 +7234,65 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>450</v>
-      </c>
       <c r="F6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>38</v>
@@ -7288,19 +7301,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>38</v>
@@ -7309,19 +7322,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>38</v>
@@ -7330,19 +7343,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>38</v>
@@ -7351,42 +7364,42 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>471</v>
-      </c>
       <c r="F11" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>38</v>
@@ -7395,19 +7408,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>38</v>
@@ -7416,19 +7429,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>38</v>
@@ -7437,19 +7450,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>484</v>
-      </c>
       <c r="E15" s="6" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>38</v>
@@ -7458,19 +7471,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>38</v>
@@ -7479,19 +7492,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>38</v>
@@ -7500,65 +7513,65 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>38</v>
@@ -7567,42 +7580,42 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>38</v>
@@ -7611,19 +7624,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="E23" s="6" t="s">
         <v>515</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>513</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>38</v>
@@ -7632,19 +7645,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>38</v>
@@ -7653,19 +7666,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>38</v>
@@ -7674,19 +7687,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>38</v>
@@ -7695,48 +7708,48 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>527</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -7811,32 +7824,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7844,19 +7857,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7864,19 +7877,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7884,19 +7897,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7904,19 +7917,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7924,19 +7937,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>559</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7944,19 +7957,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7964,19 +7977,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7984,19 +7997,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>572</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>573</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8004,19 +8017,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8024,29 +8037,29 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B17" s="22" t="n">
         <v>0.065</v>
@@ -8054,7 +8067,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B18" s="22" t="n">
         <v>0.013</v>
@@ -8062,7 +8075,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B19" s="22" t="n">
         <v>0.0033</v>
@@ -8070,55 +8083,55 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D24" s="23" t="n">
         <v>1</v>
@@ -8143,18 +8156,18 @@
         <v>0.0297</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D25" s="23" t="n">
         <v>7</v>
@@ -8179,18 +8192,18 @@
         <v>0.08085</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D26" s="23" t="n">
         <v>1</v>
@@ -8215,18 +8228,18 @@
         <v>0.0297</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D27" s="23" t="n">
         <v>7</v>
@@ -8251,18 +8264,18 @@
         <v>0.08085</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D28" s="23" t="n">
         <v>1</v>
@@ -8287,18 +8300,18 @@
         <v>0.0264</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D29" s="23" t="n">
         <v>7</v>
@@ -8323,18 +8336,18 @@
         <v>0.08085</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D30" s="23" t="n">
         <v>1</v>
@@ -8359,18 +8372,18 @@
         <v>0.0396</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D31" s="23" t="n">
         <v>1</v>
@@ -8395,12 +8408,12 @@
         <v>0.0231</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
@@ -8429,7 +8442,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="700">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -334,7 +334,7 @@
     <t xml:space="preserve">Catchy upbeat indie pop, 123 BPM</t>
   </si>
   <si>
-    <t xml:space="preserve">≈61 s (58.3 s song + end card)</t>
+    <t xml:space="preserve">54.8 s (the song; no end card)</t>
   </si>
   <si>
     <t xml:space="preserve">Anonymised retelling; permission DM drafted (in the script)</t>
@@ -379,46 +379,250 @@
     <t xml:space="preserve">Storyline + Suno prompt in tab Story &amp; Song</t>
   </si>
   <si>
+    <t xml:space="preserve">He watched his speedrun hero for years. Then, chasing a personal best with 4 viewers, the hero raided him with 450. Based on a true story.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ST-03</t>
   </si>
   <si>
+    <t xml:space="preserve">Mom talks to the stream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/comments/e2mdhf/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back to streaming for a week, he steps away to the bathroom. His mom, watching his stream, talks to the computer thinking he can hear her, then texts his girlfriend asking why he isn't answering. He laughs hard and promises to show her how chat works at Thanksgiving.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">funny, wholesome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part-timer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel art → Papercut · CRT/VHS · Kinetic type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouncy ukulele pop, 128 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50–60 s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anonymised; ask the author first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arc: complete. Facts from the post + one OP comment. Don't use commenters' stories (loss of parents).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">His mom watched his stream and talked to the screen. Nobody told her about chat. Based on a true story.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The drawing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/comments/1o4bi4r/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A regular who dropped into every few streams just to chill showed the streamer a small drawing of their character on stream. It wasn't fancy, but it made their whole week: the first time they saw that people cared about their stream, not just the game.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11, 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel art → Crayon texture (shapes) · Stained glass · Constellations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm indie folk pop, 122 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arc: complete (one moment). Thin story (5 facts): the film leans on the drawing. Viewer and game unnamed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A viewer drew the streamer's character. That's when they knew people came for them, not the game. Based on a true story.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The one who stopped coming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/comments/1bwbcvj/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A viewer came to every single stream, rain or shine, and chatted with the kindest vibes. Then one day he disappeared and never came back. The streamer misses him and hopes he's alright.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sad, open-ended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14, 11, 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grinder</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engraving → Blueprint · Thermal · Terminal/ASCII</t>
   </si>
   <si>
-    <t xml:space="preserve">50–60 s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick from the Story Fisher shortlist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pixel art → CRT/VHS · Oscilloscope · Halftone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ST-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papercut → Stained glass · Neon line · Constellations</t>
+    <t xml:space="preserve">Soft piano ballad that builds, 120 BPM (half-time feel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arc: OPEN-ENDED: no return, no reason. End on 'no answer' / to be continued. Never imply death (only commenters raised it). Post body removed: facts from the title + OP comments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He came to every stream, rain or shine. Then one day he didn't. Based on a true story.</t>
   </si>
   <si>
     <t xml:space="preserve">ST-06</t>
   </si>
   <si>
-    <t xml:space="preserve">Voxel diorama → Pixel art · Glitch · Kinetic type</t>
+    <t xml:space="preserve">They set alarms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/comments/ithm2q/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Australian streamer goes live every night from 21:30 to 2 am. His regulars are in the UK, the USA and elsewhere. This week a few of them told him they set alarms to get up and watch. Viewers thank him, which feels strange, because the stream is his happy place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8, 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constellations / particles → LED dot-matrix (clocks) · Pixel art · Neon line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dreamy synth pop, 124 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arc: complete. Leave out the weight-loss part and anything from commenters (PTSD, military, a teenager).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some of his viewers set alarms in the middle of the night to watch him. Based on a true story.</t>
   </si>
   <si>
     <t xml:space="preserve">ST-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Neon line → LED dot-matrix · Halftone · Particles</t>
+    <t xml:space="preserve">The game that died</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/comments/784qme/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He streamed to no one for four months, then found regulars one by one. A new game took him to 50 viewers and friends among players and developers. Then the game died: almost everyone left. He kept streaming, stopped watching the numbers, and grew back to 18 and more. Some days are still bad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bittersweet, triumphant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15, 16, 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscilloscope / vector glow (the viewer graph) → Data/UI · CRT/VHS · Halftone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driving alt-rock pop that drops and rebuilds, 132 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arc: complete, honest ending (OP still has bad days). Exclude his dark joke about self-harm. Don't name the game. Numbers are self-reported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 months. Zero viewers, then 50, then the game died. He kept streaming. Based on a true story.</t>
   </si>
   <si>
     <t xml:space="preserve">ST-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Halftone → Papercut · Blueprint · CRT/VHS</t>
+    <t xml:space="preserve">The karaoke mic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/comments/1i685fc/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He sings whenever music is on, and people seemed to like it, so he bought a karaoke mic and sang while playing, belting while the enemy team ran him down. He peaked at 34 viewers, his record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">funny, triumphant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7, 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel art → Kinetic type · LED dot-matrix · Halftone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power-pop karaoke anthem, 136 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arc: complete. Nobody sings on screen: the mic is the protagonist (sound waves, VU meter), the game shows him losing, the counter climbs to 34.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He bought a karaoke mic and sang while losing. 34 viewers, his record. Based on a true story.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First stream, first donation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/comments/1e4y7xf/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nervous on their first stream, they expected no one. A few friends and one or two strangers came and chatted. One viewer asked if he could donate; they said no; he insisted. It wasn't much, but it made their day, and after the stream they set up a schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wholesome, hopeful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papercut → Pixel art · Neon line · Constellations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hopeful acoustic pop, 124 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arc: complete for the moment (whether they kept the schedule is unknown: don't claim it). Amount not stated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First stream. Nervous. Expected no one. Then a stranger asked if he could donate. Based on a true story.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The algorithm stopped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.reddit.com/comments/1n4p4yb/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two weeks into streaming, the first 13 days were amazing: thousands of views, donations, a busy chat. Around day 14 the views tanked and the platform stopped showing the stream. Now barely anyone comes, and nobody stays, because they see no one else there.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15, 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data/UI → Glitch · Thermal · Terminal/ASCII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark synthwave pop whose drop cuts out, 128 BPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arc: OPEN-ENDED (no resolution). Numbers differ (100 vs 30): use 'barely anyone'. Don't claim a ban. No platform logos/UI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 days of thousands of viewers. On day 14 the algorithm stopped. Based on a true story.</t>
   </si>
   <si>
     <t xml:space="preserve">Section 2 · Brand · Generic (pain → need → function)</t>
@@ -505,9 +709,6 @@
     <t xml:space="preserve">The 40th “what rank are you?”</t>
   </si>
   <si>
-    <t xml:space="preserve">Grinder</t>
-  </si>
-  <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
@@ -586,9 +787,6 @@
     <t xml:space="preserve">4 hours → 4 clips</t>
   </si>
   <si>
-    <t xml:space="preserve">Part-timer</t>
-  </si>
-  <si>
     <t xml:space="preserve">10</t>
   </si>
   <si>
@@ -880,10 +1078,10 @@
     <t xml:space="preserve">MV</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3 s song (≈61 s film)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0:00–0:03 “Based on a true story” over a slow push into the pixel city at dusk (out on the beat). A desk-bound game streamer takes the stream on a Christmas tour of their city: market lights, a castle, a lit carousel. Viewer counter climbs to 3. At the station they are about to end the stream; chat: 'wait, I've never been on a train'. Hero shot: through the window the city falls away into open farmland, fast. The signal bars drop, freeze, black. The chat fills the frame: 'thanks for being so chill. amazing stream'. Halftone burst: 3 VIEWERS. ENOUGH. Pull back over the fields and the globe to one lit window on the other side of the world; a small spark by the message (companion cameo). Line: They kept streaming IRL. End card + credit: Story shared by a streamer on Reddit.</t>
+    <t xml:space="preserve">54.8 s (song = film)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts with the song; “Based on a true story” pops on over the desk. Desk: monitor dark, door opens, phone goes LIVE → the town at Christmas, phone on its tripod filming the carousel → neon square, 3 watching → station through the stream UI: “End stream?”, then “wait, I've never been on a train” → the train pulls out; “can you keep it on?” → the city falls away into farmland, signal bars drop → signal lost → “thanks for being so chill. amazing stream” → front page “3 VIEWERS. ENOUGH.” → globe: a line to the other side of the world → back in town → next morning: “They kept streaming IRL.” + credit. No people, no brand.</t>
   </si>
   <si>
     <t xml:space="preserve">catchy upbeat indie pop, warm and hopeful, glockenspiel hook from the first second, train-rhythm drums with handclaps, bright felt piano, clear warm vocal up front, singalong chorus, crisp modern production, 120 BPM</t>
@@ -950,16 +1148,43 @@
     <t xml:space="preserve">Full picture checked (75 comments): arc complete, no follow-ups; raid was 450 viewers while chasing a PB with 4. Never name the speedrunner. Not yet approved.</t>
   </si>
   <si>
-    <t xml:space="preserve">(pick from the Story Fisher shortlist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opens with “Based on a true story” (1.5 bars, 2.5–3 s, over the first shot). Rest written after the story is chosen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Intro: 2 bars, instrumental] …</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Written after the story is chosen</t>
+    <t xml:space="preserve">Starts with the song; the hook sticker “Based on a true story” pops on over the first shot. An empty chair and a live stream; on the other side, a phone screen with the stream and a voice bubble talking to it that never reaches him; texts pile up; he's back, laughing; Thanksgiving: two blank figures at one laptop, the chat box open. No faces: objects, UI, blank humans or simple pixel art. Ends on the story with the credit (no brand).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written after the script is approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed genre: Bouncy ukulele pop, 128 BPM. Arc: complete. Facts from the post + one OP comment. Don't use commenters' stories (loss of parents).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts with the song; the hook sticker “Based on a true story” pops on over the first shot. The game on screen, a quiet chat; one name drops in every few streams; a small crayon drawing of the character appears in chat and grows to fill the frame; the drawing turns into a stained-glass window. No faces: objects, UI, blank humans or simple pixel art. Ends on the story with the credit (no brand).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed genre: Warm indie folk pop, 122 BPM. Arc: complete (one moment). Thin story (5 facts): the film leans on the drawing. Viewer and game unnamed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts with the song; the hook sticker “Based on a true story” pops on over the first shot. The same username at the top of chat, stream after stream (rain on the window, sun, snow); one day the chat scrolls and the name doesn't come; an empty seat in the chat list; the streamer's message: hope you're alright. No faces: objects, UI, blank humans or simple pixel art. Ends on the story with the credit (no brand).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed genre: Soft piano ballad that builds, 120 BPM (half-time feel). Arc: OPEN-ENDED: no return, no reason. End on 'no answer' / to be continued. Never imply death (only commenters raised it). Post body removed: facts from the title + OP comments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts with the song; the hook sticker “Based on a true story” pops on over the first shot. Night over one city, a lit window, LIVE; the globe turns: alarm clocks ring in dark rooms in other time zones, screens light up; dot-matrix clocks in three cities; the chat fills; at 2 am he thanks everyone. No faces: objects, UI, blank humans or simple pixel art. Ends on the story with the credit (no brand).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed genre: Dreamy synth pop, 124 BPM. Arc: complete. Leave out the weight-loss part and anything from commenters (PTSD, military, a teenager).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts with the song; the hook sticker “Based on a true story” pops on over the first shot. A flat line on a viewer graph; it rises one regular at a time; a new game: the line shoots up, friends' names multiply; the game's servers go dark, the line falls; he keeps going live; the line climbs slowly, steadier. No faces: objects, UI, blank humans or simple pixel art. Ends on the story with the credit (no brand).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed genre: Driving alt-rock pop that drops and rebuilds, 132 BPM. Arc: complete, honest ending (OP still has bad days). Exclude his dark joke about self-harm. Don't name the game. Numbers are self-reported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts with the song; the hook sticker “Based on a true story” pops on over the first shot. A karaoke mic arrives in a box; the game starts, a VU meter jumps; the enemy team runs him down while the sound waves go wild; the viewer counter ticks up with every chorus to 34; a record badge. No faces: objects, UI, blank humans or simple pixel art. Ends on the story with the credit (no brand).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed genre: Power-pop karaoke anthem, 136 BPM. Arc: complete. Nobody sings on screen: the mic is the protagonist (sound waves, VU meter), the game shows him losing, the counter climbs to 34.</t>
   </si>
   <si>
     <t xml:space="preserve">A · majestic technical (instrumental)</t>
@@ -1400,6 +1625,18 @@
   </si>
   <si>
     <t xml:space="preserve">'Never live alone' is a placeholder tagline until you decide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts with the song; the hook sticker “Based on a true story” pops on over the first shot. A 'Go live' button and a shaking cursor; viewer count 0, then friends' names, then a stranger; 'can I donate?' 'no' 'please'; a small donation alert; after the stream a blank calendar fills with stream days. No faces: objects, UI, blank humans or simple pixel art. Ends on the story with the credit (no brand).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed genre: Hopeful acoustic pop, 124 BPM. Arc: complete for the moment (whether they kept the schedule is unknown: don't claim it). Amount not stated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts with the song; the hook sticker “Based on a true story” pops on over the first shot. A feed of streams scrolling fast; his stream pops up again and again, the view counter racing, chat flying; a calendar ticks to day 14; the feed scrolls past him; the counter drops; an empty chat; a cursor waiting. No faces: objects, UI, blank humans or simple pixel art. Ends on the story with the credit (no brand).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed genre: Dark synthwave pop whose drop cuts out, 128 BPM. Arc: OPEN-ENDED (no resolution). Numbers differ (100 vs 30): use 'barely anyone'. Don't claim a ban. No platform logos/UI.</t>
   </si>
   <si>
     <t xml:space="preserve">Shared assets</t>
@@ -2996,19 +3233,19 @@
         <v>14</v>
       </c>
       <c r="E6" s="6" t="n">
-        <f aca="false">COUNTA('1 Streamer Stories'!A6:A13)</f>
-        <v>8</v>
+        <f aca="false">COUNTA('1 Streamer Stories'!A6:A15)</f>
+        <v>10</v>
       </c>
       <c r="F6" s="6" t="n">
-        <f aca="false">COUNTIF('1 Streamer Stories'!M6:M13,"Approved")</f>
+        <f aca="false">COUNTIF('1 Streamer Stories'!M6:M15,"Approved")</f>
         <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <f aca="false">COUNTIF('1 Streamer Stories'!N6:N13,"Approved")</f>
+        <f aca="false">COUNTIF('1 Streamer Stories'!N6:N15,"Approved")</f>
         <v>1</v>
       </c>
       <c r="H6" s="6" t="n">
-        <f aca="false">COUNTIF('1 Streamer Stories'!Q6:Q13,"Approved")</f>
+        <f aca="false">COUNTIF('1 Streamer Stories'!Q6:Q15,"Approved")</f>
         <v>0</v>
       </c>
     </row>
@@ -3243,7 +3480,7 @@
     <tabColor rgb="FF7A5AF8"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
@@ -3263,7 +3500,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3529,28 +3766,47 @@
       <c r="U7" s="19" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V7" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
+        <v>115</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>121</v>
+      </c>
       <c r="H8" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I8" s="19"/>
+        <v>122</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>123</v>
+      </c>
       <c r="J8" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L8" s="19"/>
+        <v>124</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>125</v>
+      </c>
       <c r="M8" s="6" t="s">
         <v>38</v>
       </c>
@@ -3567,33 +3823,54 @@
         <v>38</v>
       </c>
       <c r="R8" s="19"/>
-      <c r="S8" s="6"/>
+      <c r="S8" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="T8" s="19"/>
       <c r="U8" s="19" t="s">
-        <v>117</v>
+        <v>126</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+        <v>128</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>84</v>
+      </c>
       <c r="H9" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="I9" s="19"/>
+        <v>133</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>134</v>
+      </c>
       <c r="J9" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L9" s="19"/>
+        <v>124</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>125</v>
+      </c>
       <c r="M9" s="6" t="s">
         <v>38</v>
       </c>
@@ -3610,33 +3887,54 @@
         <v>38</v>
       </c>
       <c r="R9" s="19"/>
-      <c r="S9" s="6"/>
+      <c r="S9" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="T9" s="19"/>
       <c r="U9" s="19" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>135</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
+        <v>137</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>143</v>
+      </c>
       <c r="H10" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="I10" s="19"/>
+        <v>144</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>145</v>
+      </c>
       <c r="J10" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L10" s="19"/>
+        <v>124</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>125</v>
+      </c>
       <c r="M10" s="6" t="s">
         <v>38</v>
       </c>
@@ -3653,33 +3951,54 @@
         <v>38</v>
       </c>
       <c r="R10" s="19"/>
-      <c r="S10" s="6"/>
+      <c r="S10" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="T10" s="19"/>
       <c r="U10" s="19" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>146</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
+        <v>148</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>121</v>
+      </c>
       <c r="H11" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I11" s="19"/>
+        <v>153</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>154</v>
+      </c>
       <c r="J11" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L11" s="19"/>
+        <v>124</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>125</v>
+      </c>
       <c r="M11" s="6" t="s">
         <v>38</v>
       </c>
@@ -3696,33 +4015,54 @@
         <v>38</v>
       </c>
       <c r="R11" s="19"/>
-      <c r="S11" s="6"/>
+      <c r="S11" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="T11" s="19"/>
       <c r="U11" s="19" t="s">
-        <v>117</v>
+        <v>155</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
+        <v>157</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>143</v>
+      </c>
       <c r="H12" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I12" s="19"/>
+        <v>163</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>164</v>
+      </c>
       <c r="J12" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L12" s="19"/>
+        <v>124</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>125</v>
+      </c>
       <c r="M12" s="6" t="s">
         <v>38</v>
       </c>
@@ -3739,33 +4079,54 @@
         <v>38</v>
       </c>
       <c r="R12" s="19"/>
-      <c r="S12" s="6"/>
+      <c r="S12" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="T12" s="19"/>
       <c r="U12" s="19" t="s">
-        <v>117</v>
+        <v>165</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
+        <v>167</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>84</v>
+      </c>
       <c r="H13" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="I13" s="19"/>
+        <v>173</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>174</v>
+      </c>
       <c r="J13" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="L13" s="19"/>
+        <v>124</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>125</v>
+      </c>
       <c r="M13" s="6" t="s">
         <v>38</v>
       </c>
@@ -3782,10 +4143,143 @@
         <v>38</v>
       </c>
       <c r="R13" s="19"/>
-      <c r="S13" s="6"/>
+      <c r="S13" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="T13" s="19"/>
       <c r="U13" s="19" t="s">
-        <v>117</v>
+        <v>175</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R14" s="19"/>
+      <c r="S14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R15" s="19"/>
+      <c r="S15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -3891,23 +4385,23 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M5:M13" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M5:M15" type="list">
       <formula1>"Not started,In progress,Review,Approved,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N5:N13" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="N5:N15" type="list">
       <formula1>"Not started,In progress,Review,Approved,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O5:O13" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O5:O15" type="list">
       <formula1>"Not started,In progress,Review,Approved,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P5:P13" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P5:P15" type="list">
       <formula1>"Not started,In progress,Review,Approved,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q5:Q13" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q5:Q15" type="list">
       <formula1>"Not started,In progress,Review,Approved,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3954,12 +4448,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3967,37 +4461,37 @@
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>62</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>65</v>
@@ -4032,44 +4526,44 @@
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>84</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K5" s="19"/>
       <c r="L5" s="6" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O5" s="6" t="s">
         <v>38</v>
@@ -4092,44 +4586,44 @@
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="6" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>38</v>
@@ -4152,44 +4646,44 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>158</v>
+        <v>225</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K7" s="19"/>
       <c r="L7" s="6" t="s">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>38</v>
@@ -4212,44 +4706,44 @@
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>158</v>
+        <v>225</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="6" t="s">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>38</v>
@@ -4272,44 +4766,44 @@
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>165</v>
+        <v>232</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>169</v>
+        <v>236</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="6" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>38</v>
@@ -4332,44 +4826,44 @@
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>165</v>
+        <v>232</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>169</v>
+        <v>236</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="6" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>38</v>
@@ -4392,44 +4886,44 @@
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>172</v>
+        <v>239</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="6" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>38</v>
@@ -4452,44 +4946,44 @@
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="K12" s="19"/>
       <c r="L12" s="6" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>38</v>
@@ -4512,44 +5006,44 @@
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>184</v>
+        <v>250</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>185</v>
+        <v>251</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>186</v>
+        <v>252</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="6" t="s">
-        <v>188</v>
+        <v>254</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>38</v>
@@ -4572,44 +5066,44 @@
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>184</v>
+        <v>250</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>185</v>
+        <v>251</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>186</v>
+        <v>252</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="6" t="s">
-        <v>188</v>
+        <v>254</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>38</v>
@@ -4632,44 +5126,44 @@
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>195</v>
+        <v>261</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="6" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>38</v>
@@ -4692,44 +5186,44 @@
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>195</v>
+        <v>261</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>196</v>
+        <v>262</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="6" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>38</v>
@@ -4752,44 +5246,44 @@
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>205</v>
+        <v>271</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="6" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>38</v>
@@ -4812,44 +5306,44 @@
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>202</v>
+        <v>268</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>205</v>
+        <v>271</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="6" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
@@ -4872,44 +5366,44 @@
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="C19" s="6" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>212</v>
+        <v>278</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>214</v>
+        <v>280</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>215</v>
+        <v>281</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="6" t="s">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>38</v>
@@ -4932,44 +5426,44 @@
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>217</v>
+        <v>283</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>212</v>
+        <v>278</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>214</v>
+        <v>280</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>215</v>
+        <v>281</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="6" t="s">
-        <v>216</v>
+        <v>282</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>38</v>
@@ -5151,12 +5645,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>218</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>219</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5164,13 +5658,13 @@
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>66</v>
@@ -5179,7 +5673,7 @@
         <v>65</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>221</v>
+        <v>287</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>68</v>
@@ -5208,25 +5702,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>222</v>
+        <v>288</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>225</v>
+        <v>291</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>226</v>
+        <v>292</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>227</v>
+        <v>293</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>38</v>
@@ -5246,30 +5740,30 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
       <c r="O5" s="19" t="s">
-        <v>228</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>229</v>
+        <v>295</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>230</v>
+        <v>296</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>231</v>
+        <v>297</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>225</v>
+        <v>291</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>226</v>
+        <v>292</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>232</v>
+        <v>298</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>38</v>
@@ -5289,38 +5783,38 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
       <c r="O6" s="19" t="s">
-        <v>233</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>236</v>
+        <v>302</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>237</v>
+        <v>303</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>238</v>
+        <v>304</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>239</v>
+        <v>305</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>240</v>
+        <v>306</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>241</v>
+        <v>307</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>242</v>
+        <v>308</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>76</v>
@@ -5331,22 +5825,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>243</v>
+        <v>309</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>244</v>
+        <v>310</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>246</v>
+        <v>312</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>247</v>
+        <v>313</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>248</v>
+        <v>314</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>38</v>
@@ -5358,22 +5852,22 @@
         <v>2</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>249</v>
+        <v>315</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>250</v>
+        <v>316</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>252</v>
+        <v>318</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>253</v>
+        <v>319</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>38</v>
@@ -5385,22 +5879,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>254</v>
+        <v>320</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>255</v>
+        <v>321</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>256</v>
+        <v>322</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>257</v>
+        <v>323</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>258</v>
+        <v>324</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>259</v>
+        <v>325</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>38</v>
@@ -5412,22 +5906,22 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>260</v>
+        <v>326</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>261</v>
+        <v>327</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>262</v>
+        <v>328</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>263</v>
+        <v>329</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>264</v>
+        <v>330</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>38</v>
@@ -5439,22 +5933,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>265</v>
+        <v>331</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>266</v>
+        <v>332</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>201</v>
-      </c>
       <c r="G14" s="6" t="s">
-        <v>269</v>
+        <v>335</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>38</v>
@@ -5626,7 +6120,7 @@
     <tabColor rgb="FFC2410C"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -5644,12 +6138,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>270</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>271</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5657,31 +6151,31 @@
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>272</v>
+        <v>338</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>273</v>
+        <v>339</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>274</v>
+        <v>340</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>276</v>
+        <v>342</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>277</v>
+        <v>343</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>278</v>
+        <v>344</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>76</v>
@@ -5692,34 +6186,34 @@
         <v>92</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>279</v>
+        <v>345</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>281</v>
+        <v>347</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>123</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>282</v>
+        <v>348</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>285</v>
+        <v>351</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>41</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>286</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5727,10 +6221,10 @@
         <v>103</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>287</v>
+        <v>353</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>111</v>
@@ -5739,806 +6233,900 @@
         <v>140</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>288</v>
+        <v>354</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>289</v>
+        <v>355</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>290</v>
+        <v>356</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>291</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>292</v>
+        <v>116</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>128</v>
+      </c>
       <c r="F7" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="G7" s="6"/>
+        <v>358</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="H7" s="6" t="s">
-        <v>284</v>
+        <v>359</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>294</v>
+        <v>359</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>295</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>292</v>
+        <v>129</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>122</v>
+      </c>
       <c r="F8" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="G8" s="6"/>
+        <v>361</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="H8" s="6" t="s">
-        <v>284</v>
+        <v>359</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>294</v>
+        <v>359</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>295</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="G9" s="6"/>
+        <v>363</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="H9" s="6" t="s">
-        <v>284</v>
+        <v>359</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>294</v>
+        <v>359</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>295</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>124</v>
+      </c>
       <c r="F10" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="G10" s="6"/>
+        <v>365</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="H10" s="6" t="s">
-        <v>284</v>
+        <v>359</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>294</v>
+        <v>359</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>295</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="6" t="n">
+        <v>132</v>
+      </c>
       <c r="F11" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="G11" s="6"/>
+        <v>367</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="H11" s="6" t="s">
-        <v>284</v>
+        <v>359</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>294</v>
+        <v>359</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>295</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>292</v>
+        <v>168</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>136</v>
+      </c>
       <c r="F12" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="G12" s="6"/>
+        <v>369</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>359</v>
+      </c>
       <c r="H12" s="6" t="s">
-        <v>284</v>
+        <v>359</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>294</v>
+        <v>359</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>295</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>297</v>
+        <v>372</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>298</v>
+        <v>373</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>303</v>
+        <v>378</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>304</v>
+        <v>379</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>305</v>
+        <v>380</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>307</v>
+        <v>382</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>308</v>
+        <v>383</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>309</v>
+        <v>384</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
-        <v>310</v>
+        <v>385</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>311</v>
+        <v>386</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>312</v>
+        <v>387</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>313</v>
+        <v>388</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>314</v>
+        <v>389</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>315</v>
+        <v>390</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>316</v>
+        <v>391</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>317</v>
+        <v>392</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>318</v>
+        <v>393</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>172</v>
+        <v>239</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
-        <v>319</v>
+        <v>394</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>320</v>
+        <v>395</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>321</v>
+        <v>396</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
-        <v>322</v>
+        <v>397</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>323</v>
+        <v>398</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>324</v>
+        <v>399</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6" t="s">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>326</v>
+        <v>401</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>327</v>
+        <v>402</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6" t="s">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>329</v>
+        <v>404</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>330</v>
+        <v>405</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
-        <v>331</v>
+        <v>406</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>332</v>
+        <v>407</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>333</v>
+        <v>408</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6" t="s">
-        <v>334</v>
+        <v>409</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>335</v>
+        <v>410</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>336</v>
+        <v>411</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>199</v>
+        <v>265</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6" t="s">
-        <v>337</v>
+        <v>412</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>338</v>
+        <v>413</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>339</v>
+        <v>414</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6" t="s">
-        <v>340</v>
+        <v>415</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>341</v>
+        <v>416</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>342</v>
+        <v>417</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>209</v>
+        <v>275</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6" t="s">
-        <v>343</v>
+        <v>418</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>344</v>
+        <v>419</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>345</v>
+        <v>420</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>217</v>
+        <v>283</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6" t="s">
-        <v>346</v>
+        <v>421</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>347</v>
+        <v>422</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>348</v>
+        <v>423</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>306</v>
+        <v>381</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>222</v>
+        <v>288</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>349</v>
+        <v>424</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>350</v>
+        <v>425</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>90</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>351</v>
+        <v>426</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>352</v>
+        <v>427</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>299</v>
+        <v>374</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>353</v>
+        <v>428</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>354</v>
+        <v>429</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>229</v>
+        <v>295</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>355</v>
+        <v>430</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>350</v>
+        <v>425</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>356</v>
+        <v>431</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>357</v>
+        <v>432</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>358</v>
+        <v>433</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K30" s="19" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>359</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -6564,7 +7152,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J30" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J32" type="list">
       <formula1>"Not started,In progress,Review,Approved,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6602,38 +7190,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>360</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>361</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>362</v>
+        <v>441</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>363</v>
+        <v>442</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>364</v>
+        <v>443</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>365</v>
+        <v>444</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>366</v>
+        <v>445</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>242</v>
+        <v>308</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>367</v>
+        <v>446</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>76</v>
@@ -6641,19 +7229,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>368</v>
+        <v>447</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>369</v>
+        <v>448</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>370</v>
+        <v>449</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>371</v>
+        <v>450</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>38</v>
@@ -6661,24 +7249,24 @@
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19" t="s">
-        <v>372</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>373</v>
+        <v>452</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>369</v>
+        <v>448</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>374</v>
+        <v>453</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>371</v>
+        <v>450</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>38</v>
@@ -6689,16 +7277,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>375</v>
+        <v>454</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>369</v>
+        <v>448</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>376</v>
+        <v>455</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
@@ -6710,19 +7298,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>377</v>
+        <v>456</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>369</v>
+        <v>448</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>379</v>
+        <v>458</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>38</v>
@@ -6730,21 +7318,21 @@
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19" t="s">
-        <v>380</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>381</v>
+        <v>460</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>382</v>
+        <v>461</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
@@ -6753,24 +7341,24 @@
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="19" t="s">
-        <v>383</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>384</v>
+        <v>463</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>385</v>
+        <v>464</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>386</v>
+        <v>465</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>38</v>
@@ -6778,24 +7366,24 @@
       <c r="G10" s="19"/>
       <c r="H10" s="19"/>
       <c r="I10" s="19" t="s">
-        <v>387</v>
+        <v>466</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>388</v>
+        <v>467</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>385</v>
+        <v>464</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>389</v>
+        <v>468</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>390</v>
+        <v>469</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>38</v>
@@ -6803,24 +7391,24 @@
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19" t="s">
-        <v>258</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>391</v>
+        <v>470</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>385</v>
+        <v>464</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>389</v>
+        <v>468</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>392</v>
+        <v>471</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>38</v>
@@ -6828,21 +7416,21 @@
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
       <c r="I12" s="19" t="s">
-        <v>393</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>394</v>
+        <v>473</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>385</v>
+        <v>464</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>389</v>
+        <v>468</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
@@ -6851,21 +7439,21 @@
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
       <c r="I13" s="19" t="s">
-        <v>395</v>
+        <v>474</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>396</v>
+        <v>475</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>385</v>
+        <v>464</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>397</v>
+        <v>476</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>398</v>
+        <v>477</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
@@ -6874,21 +7462,21 @@
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
       <c r="I14" s="19" t="s">
-        <v>399</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>400</v>
+        <v>479</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>401</v>
+        <v>480</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>402</v>
+        <v>481</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
@@ -6897,21 +7485,21 @@
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19" t="s">
-        <v>403</v>
+        <v>482</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>404</v>
+        <v>483</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>405</v>
+        <v>484</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>406</v>
+        <v>485</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
@@ -6920,21 +7508,21 @@
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
       <c r="I16" s="19" t="s">
-        <v>407</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>408</v>
+        <v>487</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>405</v>
+        <v>484</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>409</v>
+        <v>488</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
@@ -6943,24 +7531,24 @@
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
       <c r="I17" s="19" t="s">
-        <v>410</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>411</v>
+        <v>490</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>405</v>
+        <v>484</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>409</v>
+        <v>488</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>412</v>
+        <v>491</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>38</v>
@@ -6968,24 +7556,24 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19" t="s">
-        <v>413</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>414</v>
+        <v>493</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>415</v>
+        <v>494</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>378</v>
+        <v>457</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>386</v>
+        <v>465</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>38</v>
@@ -6993,24 +7581,24 @@
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
       <c r="I19" s="19" t="s">
-        <v>416</v>
+        <v>495</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>417</v>
+        <v>496</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>415</v>
+        <v>494</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>389</v>
+        <v>468</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>418</v>
+        <v>497</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>371</v>
+        <v>450</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>38</v>
@@ -7021,19 +7609,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>419</v>
+        <v>498</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>420</v>
+        <v>499</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>421</v>
+        <v>500</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>422</v>
+        <v>501</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>423</v>
+        <v>502</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>39</v>
@@ -7041,24 +7629,24 @@
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19" t="s">
-        <v>424</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>425</v>
+        <v>504</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>426</v>
+        <v>505</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>427</v>
+        <v>506</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>428</v>
+        <v>507</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>38</v>
@@ -7066,24 +7654,24 @@
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19" t="s">
-        <v>429</v>
+        <v>508</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>430</v>
+        <v>509</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>409</v>
+        <v>488</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>427</v>
+        <v>506</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>428</v>
+        <v>507</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>38</v>
@@ -7091,24 +7679,24 @@
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19" t="s">
-        <v>431</v>
+        <v>510</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>432</v>
+        <v>511</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>409</v>
+        <v>488</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>433</v>
+        <v>512</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>428</v>
+        <v>507</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>38</v>
@@ -7116,21 +7704,21 @@
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19" t="s">
-        <v>434</v>
+        <v>513</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>435</v>
+        <v>514</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>436</v>
+        <v>515</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>437</v>
+        <v>516</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>438</v>
+        <v>517</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6" t="s">
@@ -7139,7 +7727,7 @@
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19" t="s">
-        <v>439</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -7201,32 +7789,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>440</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>441</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>442</v>
+        <v>521</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>443</v>
+        <v>522</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>444</v>
+        <v>523</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>445</v>
+        <v>524</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>446</v>
+        <v>525</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>447</v>
+        <v>526</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>76</v>
@@ -7234,65 +7822,65 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>448</v>
+        <v>527</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>450</v>
+        <v>529</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>451</v>
+        <v>530</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>452</v>
+        <v>531</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>453</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>454</v>
+        <v>533</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>455</v>
+        <v>534</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>456</v>
+        <v>535</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>452</v>
+        <v>531</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>457</v>
+        <v>536</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>458</v>
+        <v>537</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>459</v>
+        <v>538</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>460</v>
+        <v>539</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>461</v>
+        <v>540</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>38</v>
@@ -7301,19 +7889,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>462</v>
+        <v>541</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>463</v>
+        <v>542</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>464</v>
+        <v>543</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>465</v>
+        <v>544</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>38</v>
@@ -7322,19 +7910,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>466</v>
+        <v>545</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>467</v>
+        <v>546</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>468</v>
+        <v>547</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>469</v>
+        <v>548</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>38</v>
@@ -7343,19 +7931,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>470</v>
+        <v>549</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>471</v>
+        <v>550</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>472</v>
+        <v>551</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>473</v>
+        <v>552</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>38</v>
@@ -7364,42 +7952,42 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>474</v>
+        <v>553</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>475</v>
+        <v>554</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>476</v>
+        <v>555</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>473</v>
+        <v>552</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>477</v>
+        <v>556</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>478</v>
+        <v>557</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>479</v>
+        <v>558</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>480</v>
+        <v>559</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>465</v>
+        <v>544</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>38</v>
@@ -7408,19 +7996,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>481</v>
+        <v>560</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>482</v>
+        <v>561</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>483</v>
+        <v>562</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>469</v>
+        <v>548</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>38</v>
@@ -7429,19 +8017,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>484</v>
+        <v>563</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>485</v>
+        <v>564</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>486</v>
+        <v>565</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>487</v>
+        <v>566</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>38</v>
@@ -7450,19 +8038,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>488</v>
+        <v>567</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>489</v>
+        <v>568</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>486</v>
+        <v>565</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>469</v>
+        <v>548</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>38</v>
@@ -7471,19 +8059,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>490</v>
+        <v>569</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>491</v>
+        <v>570</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>472</v>
+        <v>551</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>461</v>
+        <v>540</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>38</v>
@@ -7492,19 +8080,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>492</v>
+        <v>571</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>493</v>
+        <v>572</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>476</v>
+        <v>555</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>494</v>
+        <v>573</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>38</v>
@@ -7513,65 +8101,65 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>495</v>
+        <v>574</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>496</v>
+        <v>575</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>497</v>
+        <v>576</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>452</v>
+        <v>531</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>498</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>499</v>
+        <v>578</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>500</v>
+        <v>579</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>501</v>
+        <v>580</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>452</v>
+        <v>531</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>502</v>
+        <v>581</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>503</v>
+        <v>582</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>504</v>
+        <v>583</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>505</v>
+        <v>584</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>473</v>
+        <v>552</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>38</v>
@@ -7580,42 +8168,42 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>506</v>
+        <v>585</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>507</v>
+        <v>586</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>508</v>
+        <v>587</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>509</v>
+        <v>588</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>510</v>
+        <v>589</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>511</v>
+        <v>590</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>512</v>
+        <v>591</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>513</v>
+        <v>592</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>514</v>
+        <v>593</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>515</v>
+        <v>594</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>38</v>
@@ -7624,19 +8212,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>516</v>
+        <v>595</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>512</v>
+        <v>591</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>517</v>
+        <v>596</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>514</v>
+        <v>593</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>515</v>
+        <v>594</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>38</v>
@@ -7645,19 +8233,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>518</v>
+        <v>597</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>512</v>
+        <v>591</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>519</v>
+        <v>598</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>514</v>
+        <v>593</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>520</v>
+        <v>599</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>38</v>
@@ -7666,19 +8254,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>521</v>
+        <v>600</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>512</v>
+        <v>591</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>522</v>
+        <v>601</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>523</v>
+        <v>602</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>515</v>
+        <v>594</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>38</v>
@@ -7687,19 +8275,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>524</v>
+        <v>603</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>512</v>
+        <v>591</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>525</v>
+        <v>604</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>526</v>
+        <v>605</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>520</v>
+        <v>599</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>38</v>
@@ -7708,48 +8296,48 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>527</v>
+        <v>606</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>528</v>
+        <v>607</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>529</v>
+        <v>608</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>529</v>
+        <v>608</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>529</v>
+        <v>608</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>530</v>
+        <v>609</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>531</v>
+        <v>610</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>528</v>
+        <v>607</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>529</v>
+        <v>608</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>529</v>
+        <v>608</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>529</v>
+        <v>608</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>532</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -7824,32 +8412,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>533</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>534</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>535</v>
+        <v>614</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>536</v>
+        <v>615</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>537</v>
+        <v>616</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>538</v>
+        <v>617</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>539</v>
+        <v>618</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>540</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7857,19 +8445,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>541</v>
+        <v>620</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>542</v>
+        <v>621</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>543</v>
+        <v>622</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>544</v>
+        <v>623</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>545</v>
+        <v>624</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7877,19 +8465,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>546</v>
+        <v>625</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>547</v>
+        <v>626</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>548</v>
+        <v>627</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>549</v>
+        <v>628</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>550</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7897,19 +8485,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>551</v>
+        <v>630</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>552</v>
+        <v>631</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>553</v>
+        <v>632</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>554</v>
+        <v>633</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>555</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7917,19 +8505,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>556</v>
+        <v>635</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>557</v>
+        <v>636</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>558</v>
+        <v>637</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>559</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7937,19 +8525,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>560</v>
+        <v>639</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>561</v>
+        <v>640</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>562</v>
+        <v>641</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>563</v>
+        <v>642</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>559</v>
+        <v>638</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7957,19 +8545,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>564</v>
+        <v>643</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>565</v>
+        <v>644</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>566</v>
+        <v>645</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>567</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7977,19 +8565,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>568</v>
+        <v>647</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>569</v>
+        <v>648</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>570</v>
+        <v>649</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>571</v>
+        <v>650</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>572</v>
+        <v>651</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7997,19 +8585,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>573</v>
+        <v>652</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>574</v>
+        <v>653</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>575</v>
+        <v>654</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>576</v>
+        <v>655</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>572</v>
+        <v>651</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8017,19 +8605,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>577</v>
+        <v>656</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>578</v>
+        <v>657</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>579</v>
+        <v>658</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>580</v>
+        <v>659</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>581</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8037,29 +8625,29 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>582</v>
+        <v>661</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>583</v>
+        <v>662</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>584</v>
+        <v>663</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>585</v>
+        <v>664</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>586</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>587</v>
+        <v>666</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>588</v>
+        <v>667</v>
       </c>
       <c r="B17" s="22" t="n">
         <v>0.065</v>
@@ -8067,7 +8655,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>589</v>
+        <v>668</v>
       </c>
       <c r="B18" s="22" t="n">
         <v>0.013</v>
@@ -8075,7 +8663,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>590</v>
+        <v>669</v>
       </c>
       <c r="B19" s="22" t="n">
         <v>0.0033</v>
@@ -8083,55 +8671,55 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>591</v>
+        <v>670</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>592</v>
+        <v>671</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>593</v>
+        <v>672</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>535</v>
+        <v>614</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>594</v>
+        <v>673</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>595</v>
+        <v>674</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>596</v>
+        <v>675</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>597</v>
+        <v>676</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>598</v>
+        <v>677</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>599</v>
+        <v>678</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>600</v>
+        <v>679</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>601</v>
+        <v>680</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>602</v>
+        <v>681</v>
       </c>
       <c r="D24" s="23" t="n">
         <v>1</v>
@@ -8156,18 +8744,18 @@
         <v>0.0297</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>603</v>
+        <v>682</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>604</v>
+        <v>683</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>602</v>
+        <v>681</v>
       </c>
       <c r="D25" s="23" t="n">
         <v>7</v>
@@ -8192,18 +8780,18 @@
         <v>0.08085</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>605</v>
+        <v>684</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>606</v>
+        <v>685</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>607</v>
+        <v>686</v>
       </c>
       <c r="D26" s="23" t="n">
         <v>1</v>
@@ -8228,18 +8816,18 @@
         <v>0.0297</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>608</v>
+        <v>687</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>609</v>
+        <v>688</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>607</v>
+        <v>686</v>
       </c>
       <c r="D27" s="23" t="n">
         <v>7</v>
@@ -8264,18 +8852,18 @@
         <v>0.08085</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>610</v>
+        <v>689</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>611</v>
+        <v>690</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>602</v>
+        <v>681</v>
       </c>
       <c r="D28" s="23" t="n">
         <v>1</v>
@@ -8300,18 +8888,18 @@
         <v>0.0264</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>612</v>
+        <v>691</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>613</v>
+        <v>692</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>602</v>
+        <v>681</v>
       </c>
       <c r="D29" s="23" t="n">
         <v>7</v>
@@ -8336,18 +8924,18 @@
         <v>0.08085</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>614</v>
+        <v>693</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>222</v>
+        <v>288</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>615</v>
+        <v>694</v>
       </c>
       <c r="D30" s="23" t="n">
         <v>1</v>
@@ -8372,18 +8960,18 @@
         <v>0.0396</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>616</v>
+        <v>695</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>229</v>
+        <v>295</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>617</v>
+        <v>696</v>
       </c>
       <c r="D31" s="23" t="n">
         <v>1</v>
@@ -8408,12 +8996,12 @@
         <v>0.0231</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>618</v>
+        <v>697</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>619</v>
+        <v>698</v>
       </c>
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
@@ -8442,7 +9030,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>620</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -3689,10 +3689,10 @@
         <v>41</v>
       </c>
       <c r="P6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q6" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="R6" s="19"/>
       <c r="S6" s="6" t="s">

--- a/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
+++ b/brand-video/plan/Chobbot_Media_Plan_v0.1.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="701">
   <si>
     <t xml:space="preserve">Chobbot media plan · v0.1 (mockup)</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t xml:space="preserve">Anonymised retelling; permission DM drafted (in the script)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In review (1080p60 done)</t>
   </si>
   <si>
     <t xml:space="preserve">Script: docs/scripts/ST-01_train-ride.md · 2026-10-04: song approved (master song_with_intro.wav); script v0.7 retimed. Next: style frames. · 2026-10-04: style frames approved (13 scenes, no on-screen people, the phone is the protagonist); quality band 6–10. Animatic rendering.</t>
@@ -3692,7 +3695,7 @@
         <v>41</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="R6" s="19"/>
       <c r="S6" s="6" t="s">
@@ -3700,48 +3703,48 @@
       </c>
       <c r="T6" s="19"/>
       <c r="U6" s="19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G7" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L7" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>38</v>
@@ -3764,48 +3767,48 @@
       </c>
       <c r="T7" s="19"/>
       <c r="U7" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>38</v>
@@ -3828,48 +3831,48 @@
       </c>
       <c r="T8" s="19"/>
       <c r="U8" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>82</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G9" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>38</v>
@@ -3892,48 +3895,48 @@
       </c>
       <c r="T9" s="19"/>
       <c r="U9" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L10" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>38</v>
@@ -3956,48 +3959,48 @@
       </c>
       <c r="T10" s="19"/>
       <c r="U10" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>82</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>38</v>
@@ -4020,48 +4023,48 @@
       </c>
       <c r="T11" s="19"/>
       <c r="U11" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>38</v>
@@ -4084,48 +4087,48 @@
       </c>
       <c r="T12" s="19"/>
       <c r="U12" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G13" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>38</v>
@@ -4148,48 +4151,48 @@
       </c>
       <c r="T13" s="19"/>
       <c r="U13" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G14" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L14" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>38</v>
@@ -4212,48 +4215,48 @@
       </c>
       <c r="T14" s="19"/>
       <c r="U14" s="19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G15" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>87</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L15" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>38</v>
@@ -4276,10 +4279,10 @@
       </c>
       <c r="T15" s="19"/>
       <c r="U15" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -4448,12 +4451,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4461,37 +4464,37 @@
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>62</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>65</v>
@@ -4526,44 +4529,44 @@
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>84</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K5" s="19"/>
       <c r="L5" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O5" s="6" t="s">
         <v>38</v>
@@ -4586,44 +4589,44 @@
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K6" s="19"/>
       <c r="L6" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>38</v>
@@ -4646,44 +4649,44 @@
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K7" s="19"/>
       <c r="L7" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>38</v>
@@ -4706,44 +4709,44 @@
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K8" s="19"/>
       <c r="L8" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>38</v>
@@ -4766,44 +4769,44 @@
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>38</v>
@@ -4826,44 +4829,44 @@
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K10" s="19"/>
       <c r="L10" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>38</v>
@@ -4886,44 +4889,44 @@
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>38</v>
@@ -4946,44 +4949,44 @@
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K12" s="19"/>
       <c r="L12" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>38</v>
@@ -5006,44 +5009,44 @@
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>38</v>
@@ -5066,44 +5069,44 @@
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>38</v>
@@ -5126,44 +5129,44 @@
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>38</v>
@@ -5186,44 +5189,44 @@
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>38</v>
@@ -5246,44 +5249,44 @@
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>38</v>
@@ -5306,44 +5309,44 @@
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
@@ -5366,44 +5369,44 @@
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>38</v>
@@ -5426,44 +5429,44 @@
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>38</v>
@@ -5645,12 +5648,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5658,13 +5661,13 @@
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>66</v>
@@ -5673,7 +5676,7 @@
         <v>65</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>68</v>
@@ -5702,25 +5705,25 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>38</v>
@@ -5740,30 +5743,30 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
       <c r="O5" s="19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>38</v>
@@ -5783,38 +5786,38 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
       <c r="O6" s="19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>76</v>
@@ -5825,22 +5828,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>38</v>
@@ -5852,22 +5855,22 @@
         <v>2</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>38</v>
@@ -5879,22 +5882,22 @@
         <v>3</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>38</v>
@@ -5906,22 +5909,22 @@
         <v>4</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>38</v>
@@ -5933,22 +5936,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>38</v>
@@ -6138,12 +6141,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6151,31 +6154,31 @@
         <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>76</v>
@@ -6186,947 +6189,947 @@
         <v>92</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>123</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>41</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>140</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>128</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>122</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>120</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>124</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>132</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K11" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>136</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="168.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K19" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K21" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K23" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K25" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K26" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="156" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K27" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="298.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K28" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>90</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="408.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>124</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K31" s="19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -7190,38 +7193,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>76</v>
@@ -7229,19 +7232,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>38</v>
@@ -7249,24 +7252,24 @@
       <c r="G5" s="19"/>
       <c r="H5" s="19"/>
       <c r="I5" s="19" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>38</v>
@@ -7277,16 +7280,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
@@ -7298,19 +7301,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>38</v>
@@ -7318,21 +7321,21 @@
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
       <c r="I8" s="19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6" t="s">
@@ -7341,24 +7344,24 @@
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
       <c r="I9" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>38</v>
@@ -7366,24 +7369,24 @@
       <c r="G10" s="19"/>
       <c r="H10" s="19"/>
       <c r="I10" s="19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>38</v>
@@ -7391,24 +7394,24 @@
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
       <c r="I11" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>38</v>
@@ -7416,21 +7419,21 @@
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
       <c r="I12" s="19" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
@@ -7439,21 +7442,21 @@
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
       <c r="I13" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
@@ -7462,21 +7465,21 @@
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
       <c r="I14" s="19" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
@@ -7485,21 +7488,21 @@
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6" t="s">
@@ -7508,21 +7511,21 @@
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
       <c r="I16" s="19" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6" t="s">
@@ -7531,24 +7534,24 @@
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
       <c r="I17" s="19" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>38</v>
@@ -7556,24 +7559,24 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>38</v>
@@ -7581,24 +7584,24 @@
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
       <c r="I19" s="19" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>38</v>
@@ -7609,19 +7612,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>39</v>
@@ -7629,24 +7632,24 @@
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>38</v>
@@ -7654,24 +7657,24 @@
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>38</v>
@@ -7679,24 +7682,24 @@
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>38</v>
@@ -7704,21 +7707,21 @@
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6" t="s">
@@ -7727,7 +7730,7 @@
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -7789,32 +7792,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>76</v>
@@ -7822,65 +7825,65 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>38</v>
@@ -7889,19 +7892,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>38</v>
@@ -7910,19 +7913,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>38</v>
@@ -7931,19 +7934,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>38</v>
@@ -7952,42 +7955,42 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>552</v>
-      </c>
       <c r="F11" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>38</v>
@@ -7996,19 +7999,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>38</v>
@@ -8017,19 +8020,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>38</v>
@@ -8038,19 +8041,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>38</v>
@@ -8059,19 +8062,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>38</v>
@@ -8080,19 +8083,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>38</v>
@@ -8101,65 +8104,65 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>38</v>
@@ -8168,42 +8171,42 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>38</v>
@@ -8212,19 +8215,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>595</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>594</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>38</v>
@@ -8233,19 +8236,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>38</v>
@@ -8254,19 +8257,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>38</v>
@@ -8275,19 +8278,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>38</v>
@@ -8296,48 +8299,48 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -8412,32 +8415,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8445,19 +8448,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8465,19 +8468,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8485,19 +8488,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8505,19 +8508,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8525,19 +8528,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>639</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>640</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>641</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8545,19 +8548,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8565,19 +8568,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8585,19 +8588,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>652</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>653</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>655</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8605,19 +8608,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8625,29 +8628,29 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B17" s="22" t="n">
         <v>0.065</v>
@@ -8655,7 +8658,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B18" s="22" t="n">
         <v>0.013</v>
@@ -8663,7 +8666,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B19" s="22" t="n">
         <v>0.0033</v>
@@ -8671,55 +8674,55 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D24" s="23" t="n">
         <v>1</v>
@@ -8744,18 +8747,18 @@
         <v>0.0297</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D25" s="23" t="n">
         <v>7</v>
@@ -8780,18 +8783,18 @@
         <v>0.08085</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D26" s="23" t="n">
         <v>1</v>
@@ -8816,18 +8819,18 @@
         <v>0.0297</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D27" s="23" t="n">
         <v>7</v>
@@ -8852,18 +8855,18 @@
         <v>0.08085</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D28" s="23" t="n">
         <v>1</v>
@@ -8888,18 +8891,18 @@
         <v>0.0264</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D29" s="23" t="n">
         <v>7</v>
@@ -8924,18 +8927,18 @@
         <v>0.08085</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D30" s="23" t="n">
         <v>1</v>
@@ -8960,18 +8963,18 @@
         <v>0.0396</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D31" s="23" t="n">
         <v>1</v>
@@ -8996,12 +8999,12 @@
         <v>0.0231</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
@@ -9030,7 +9033,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
